--- a/procurement/Amber_Jar_Sourcing_Analysis.xlsx
+++ b/procurement/Amber_Jar_Sourcing_Analysis.xlsx
@@ -753,7 +753,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="550">
   <si>
     <t xml:space="preserve">Cocoon Supplements – Amber Straight-Sided Jar Sourcing</t>
   </si>
@@ -1263,6 +1263,9 @@
   </si>
   <si>
     <t xml:space="preserve">• 90ct: a 9 oz (266 ml) jar works for size 0 or 00. A 250 ml jar works but is close to the limit for size 00. An 8 oz is tight for size 00.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 90ct if size 0: fits a 6 oz (~81% full, but tight – ~94% of space incl. headspace) or a 190 ml (comfortable). This is what makes the owner's flex plan work: buy 6 oz now and pour-test at production.</t>
   </si>
   <si>
     <t xml:space="preserve">• So every option now needs three jar sizes: ~4 oz, ~6 oz and ~9 oz. Lines with only 4 + 8/9 oz (Uline, Richards, Liquid Bottles) can't do the 60ct.</t>
@@ -3768,14 +3771,14 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="20" t="str">
-        <f aca="false">"  Cost (regular): ~CAD "&amp;TEXT('Split Plan – Local vs China'!C7,"#,##0")&amp;"–"&amp;TEXT('Split Plan – Local vs China'!C8,"#,##0")&amp;" vs ~CAD "&amp;TEXT('Split Plan – Local vs China'!C6,"#,##0")&amp;" all-local. Close to break-even, but all-local forces you to guess the 90ct jar now."</f>
-        <v>  Cost (regular): ~CAD 7,091–6,936 vs ~CAD 6,696 all-local. Close to break-even, but all-local forces you to guess the 90ct jar now.</v>
+        <f aca="false">"  Cost (regular): ~CAD "&amp;TEXT('Split Plan – Local vs China'!C8,"#,##0")&amp;"–"&amp;TEXT('Split Plan – Local vs China'!C7,"#,##0")&amp;" vs ~CAD "&amp;TEXT('Split Plan – Local vs China'!C6,"#,##0")&amp;" all-local. Close to break-even, but all-local forces you to guess the 90ct jar now."</f>
+        <v>  Cost (regular): ~CAD 6,936–7,091 vs ~CAD 6,696 all-local. Close to break-even, but all-local forces you to guess the 90ct jar now.</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="20" t="str">
-        <f aca="false">"  Cost (frosted): ~CAD "&amp;TEXT('Split Plan – Local vs China'!C13,"#,##0")&amp;"–"&amp;TEXT('Split Plan – Local vs China'!C14,"#,##0")&amp;" vs ~CAD "&amp;TEXT('Split Plan – Local vs China'!C12,"#,##0")&amp;" all-local – a clear saving."</f>
-        <v>  Cost (frosted): ~CAD 9,272–9,172 vs ~CAD 11,646 all-local – a clear saving.</v>
+        <f aca="false">"  Cost (frosted): ~CAD "&amp;TEXT('Split Plan – Local vs China'!C14,"#,##0")&amp;"–"&amp;TEXT('Split Plan – Local vs China'!C13,"#,##0")&amp;" vs ~CAD "&amp;TEXT('Split Plan – Local vs China'!C12,"#,##0")&amp;" all-local – a clear saving."</f>
+        <v>  Cost (frosted): ~CAD 9,172–9,272 vs ~CAD 11,646 all-local – a clear saving.</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4143,7 +4146,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -4905,6 +4908,11 @@
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="20" t="s">
         <v>171</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="20" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -4968,17 +4976,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -5004,7 +5012,7 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -5030,81 +5038,81 @@
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>142</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D7" s="34" t="s">
         <v>143</v>
@@ -5114,7 +5122,7 @@
         <v>2000</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G7" s="41" t="n">
         <v>11.45</v>
@@ -5127,7 +5135,7 @@
         <v>0.477083333333333</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K7" s="42" t="n">
         <v>0.14</v>
@@ -5172,18 +5180,18 @@
         <v>2.309425</v>
       </c>
       <c r="V7" s="45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>145</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D8" s="34" t="s">
         <v>146</v>
@@ -5193,7 +5201,7 @@
         <v>2000</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G8" s="41" t="n">
         <v>6.07</v>
@@ -5206,7 +5214,7 @@
         <v>0.505833333333333</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K8" s="42" t="n">
         <v>0.11</v>
@@ -5251,18 +5259,18 @@
         <v>2.31115</v>
       </c>
       <c r="V8" s="45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B9" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>150</v>
@@ -5272,7 +5280,7 @@
         <v>2000</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G9" s="41" t="n">
         <v>5.24</v>
@@ -5285,7 +5293,7 @@
         <v>0.436666666666667</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K9" s="42" t="n">
         <v>0.15</v>
@@ -5330,12 +5338,12 @@
         <v>2.3514</v>
       </c>
       <c r="V9" s="45" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B10" s="47"/>
       <c r="C10" s="47"/>
@@ -5379,19 +5387,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O11" s="44" t="n">
         <f aca="false">Inputs!$B$15*Inputs!$B$7+Inputs!$B$16</f>
         <v>1674</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -5417,7 +5425,7 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="38" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B14" s="38"/>
       <c r="C14" s="38"/>
@@ -5443,81 +5451,81 @@
     </row>
     <row r="15" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>142</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>143</v>
@@ -5527,7 +5535,7 @@
         <v>2000</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G16" s="41" t="n">
         <v>12.15</v>
@@ -5540,7 +5548,7 @@
         <v>0.50625</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K16" s="42" t="n">
         <v>0.1136</v>
@@ -5585,18 +5593,18 @@
         <v>2.305607</v>
       </c>
       <c r="V16" s="45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>145</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>146</v>
@@ -5606,7 +5614,7 @@
         <v>2000</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G17" s="41" t="n">
         <v>7.4</v>
@@ -5619,7 +5627,7 @@
         <v>0.616666666666667</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K17" s="42" t="n">
         <v>0.1444</v>
@@ -5664,18 +5672,18 @@
         <v>2.110728</v>
       </c>
       <c r="V17" s="45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D18" s="34" t="s">
         <v>150</v>
@@ -5685,7 +5693,7 @@
         <v>2000</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G18" s="41" t="n">
         <v>5.6</v>
@@ -5698,7 +5706,7 @@
         <v>0.466666666666667</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K18" s="42" t="n">
         <v>0.22</v>
@@ -5743,12 +5751,12 @@
         <v>2.2134</v>
       </c>
       <c r="V18" s="45" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
@@ -5792,19 +5800,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O20" s="44" t="n">
         <f aca="false">Inputs!$B$15*Inputs!$B$7+Inputs!$B$16</f>
         <v>1674</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -5830,7 +5838,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -5856,101 +5864,101 @@
     </row>
     <row r="24" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E25" s="39" t="n">
         <f aca="false">Inputs!$B$5</f>
         <v>2000</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G25" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H25" s="23"/>
       <c r="I25" s="42" t="n">
         <v>0.4</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K25" s="42" t="n">
         <v>0.04</v>
@@ -5994,38 +6002,38 @@
         <v>2.41946666666667</v>
       </c>
       <c r="V25" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D26" s="34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E26" s="39" t="n">
         <f aca="false">Inputs!$B$5</f>
         <v>2000</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G26" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H26" s="23"/>
       <c r="I26" s="42" t="n">
         <v>0.4</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K26" s="42" t="n">
         <v>0.04</v>
@@ -6069,18 +6077,18 @@
         <v>2.41946666666667</v>
       </c>
       <c r="V26" s="45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D27" s="34" t="s">
         <v>150</v>
@@ -6090,17 +6098,17 @@
         <v>2000</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G27" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H27" s="23"/>
       <c r="I27" s="42" t="n">
         <v>0.42</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K27" s="42" t="n">
         <v>0.04</v>
@@ -6144,12 +6152,12 @@
         <v>2.39186666666667</v>
       </c>
       <c r="V27" s="45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B28" s="47"/>
       <c r="C28" s="47"/>
@@ -6193,19 +6201,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O29" s="44" t="n">
         <f aca="false">Inputs!$B$18+Inputs!$B$26</f>
         <v>2480</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -6231,7 +6239,7 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="38" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B32" s="38"/>
       <c r="C32" s="38"/>
@@ -6257,81 +6265,81 @@
     </row>
     <row r="33" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>142</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D34" s="34" t="s">
         <v>143</v>
@@ -6341,10 +6349,10 @@
         <v>2000</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G34" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H34" s="23" t="n">
         <v>24</v>
@@ -6353,7 +6361,7 @@
         <v>0.96</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K34" s="42" t="n">
         <v>0.25</v>
@@ -6397,18 +6405,18 @@
         <v>2.16333333333333</v>
       </c>
       <c r="V34" s="45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D35" s="34" t="s">
         <v>150</v>
@@ -6418,10 +6426,10 @@
         <v>2000</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H35" s="23" t="n">
         <v>12</v>
@@ -6430,7 +6438,7 @@
         <v>0.99</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K35" s="42" t="n">
         <v>0.25</v>
@@ -6474,18 +6482,18 @@
         <v>2.13333333333333</v>
       </c>
       <c r="V35" s="45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D36" s="34" t="s">
         <v>150</v>
@@ -6495,10 +6503,10 @@
         <v>2000</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G36" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H36" s="23" t="n">
         <v>12</v>
@@ -6507,7 +6515,7 @@
         <v>0.99</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K36" s="42" t="n">
         <v>0.25</v>
@@ -6551,12 +6559,12 @@
         <v>2.13333333333333</v>
       </c>
       <c r="V36" s="45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B37" s="47"/>
       <c r="C37" s="47"/>
@@ -6600,19 +6608,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O38" s="44" t="n">
         <f aca="false">Inputs!$B$17</f>
         <v>400</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -6638,7 +6646,7 @@
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="38" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B41" s="38"/>
       <c r="C41" s="38"/>
@@ -6664,81 +6672,81 @@
     </row>
     <row r="42" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O42" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P42" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U42" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V42" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>142</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D43" s="34" t="s">
         <v>143</v>
@@ -6748,10 +6756,10 @@
         <v>2000</v>
       </c>
       <c r="F43" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G43" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H43" s="23" t="n">
         <v>24</v>
@@ -6760,7 +6768,7 @@
         <v>1.67</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K43" s="42" t="n">
         <v>0</v>
@@ -6804,18 +6812,18 @@
         <v>1.70333333333333</v>
       </c>
       <c r="V43" s="45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>149</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D44" s="34" t="s">
         <v>150</v>
@@ -6825,10 +6833,10 @@
         <v>2000</v>
       </c>
       <c r="F44" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G44" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H44" s="23" t="n">
         <v>24</v>
@@ -6837,7 +6845,7 @@
         <v>2.35</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K44" s="42" t="n">
         <v>0</v>
@@ -6881,18 +6889,18 @@
         <v>1.02333333333333</v>
       </c>
       <c r="V44" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>149</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D45" s="34" t="s">
         <v>150</v>
@@ -6902,10 +6910,10 @@
         <v>2000</v>
       </c>
       <c r="F45" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G45" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H45" s="23" t="n">
         <v>24</v>
@@ -6914,7 +6922,7 @@
         <v>2.35</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K45" s="42" t="n">
         <v>0</v>
@@ -6958,12 +6966,12 @@
         <v>1.02333333333333</v>
       </c>
       <c r="V45" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B46" s="47"/>
       <c r="C46" s="47"/>
@@ -7007,14 +7015,14 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O47" s="44" t="n">
         <f aca="false">Inputs!$B$17</f>
         <v>400</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -7071,17 +7079,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7107,7 +7115,7 @@
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B5" s="38"/>
       <c r="C5" s="38"/>
@@ -7133,101 +7141,101 @@
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P6" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E7" s="39" t="n">
         <f aca="false">Inputs!$B$5</f>
         <v>2000</v>
       </c>
       <c r="F7" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G7" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H7" s="23"/>
       <c r="I7" s="42" t="n">
         <v>0.46</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K7" s="42" t="n">
         <v>0.04</v>
@@ -7271,38 +7279,38 @@
         <v>2.33666666666667</v>
       </c>
       <c r="V7" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E8" s="39" t="n">
         <f aca="false">Inputs!$B$5</f>
         <v>2000</v>
       </c>
       <c r="F8" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G8" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H8" s="23"/>
       <c r="I8" s="42" t="n">
         <v>0.48</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K8" s="42" t="n">
         <v>0.04</v>
@@ -7346,18 +7354,18 @@
         <v>2.30906666666667</v>
       </c>
       <c r="V8" s="45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D9" s="34" t="s">
         <v>150</v>
@@ -7367,17 +7375,17 @@
         <v>2000</v>
       </c>
       <c r="F9" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H9" s="23"/>
       <c r="I9" s="42" t="n">
         <v>0.48</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K9" s="42" t="n">
         <v>0.04</v>
@@ -7421,12 +7429,12 @@
         <v>2.30906666666667</v>
       </c>
       <c r="V9" s="45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B10" s="47"/>
       <c r="C10" s="47"/>
@@ -7470,19 +7478,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O11" s="44" t="n">
         <f aca="false">Inputs!$B$18+Inputs!$B$26</f>
         <v>2480</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -7508,7 +7516,7 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="38" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B14" s="38"/>
       <c r="C14" s="38"/>
@@ -7534,81 +7542,81 @@
     </row>
     <row r="15" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P15" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>142</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D16" s="34" t="s">
         <v>143</v>
@@ -7618,7 +7626,7 @@
         <v>2000</v>
       </c>
       <c r="F16" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G16" s="41" t="n">
         <v>11.45</v>
@@ -7631,7 +7639,7 @@
         <v>0.477083333333333</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K16" s="42" t="n">
         <v>0.14</v>
@@ -7677,18 +7685,18 @@
         <v>1.484425</v>
       </c>
       <c r="V16" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" s="13" t="s">
         <v>145</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D17" s="34" t="s">
         <v>146</v>
@@ -7698,7 +7706,7 @@
         <v>2000</v>
       </c>
       <c r="F17" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G17" s="41" t="n">
         <v>6.07</v>
@@ -7711,7 +7719,7 @@
         <v>0.505833333333333</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K17" s="42" t="n">
         <v>0.11</v>
@@ -7757,18 +7765,18 @@
         <v>1.48615</v>
       </c>
       <c r="V17" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D18" s="34" t="s">
         <v>150</v>
@@ -7778,7 +7786,7 @@
         <v>2000</v>
       </c>
       <c r="F18" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G18" s="41" t="n">
         <v>5.24</v>
@@ -7791,7 +7799,7 @@
         <v>0.436666666666667</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K18" s="42" t="n">
         <v>0.15</v>
@@ -7837,12 +7845,12 @@
         <v>1.5264</v>
       </c>
       <c r="V18" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" s="47"/>
       <c r="C19" s="47"/>
@@ -7886,19 +7894,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O20" s="44" t="n">
         <f aca="false">Inputs!$B$15*Inputs!$B$7+Inputs!$B$16+Inputs!$B$34*Inputs!$B$6+Inputs!$B$35</f>
         <v>3924</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -7924,7 +7932,7 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -7950,81 +7958,81 @@
     </row>
     <row r="24" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>142</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D25" s="34" t="s">
         <v>143</v>
@@ -8034,7 +8042,7 @@
         <v>2000</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G25" s="41" t="n">
         <v>12.15</v>
@@ -8047,7 +8055,7 @@
         <v>0.50625</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K25" s="42" t="n">
         <v>0.1136</v>
@@ -8093,18 +8101,18 @@
         <v>1.480607</v>
       </c>
       <c r="V25" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>145</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D26" s="34" t="s">
         <v>146</v>
@@ -8114,7 +8122,7 @@
         <v>2000</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G26" s="41" t="n">
         <v>7.4</v>
@@ -8127,7 +8135,7 @@
         <v>0.616666666666667</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K26" s="42" t="n">
         <v>0.1444</v>
@@ -8173,18 +8181,18 @@
         <v>1.285728</v>
       </c>
       <c r="V26" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D27" s="34" t="s">
         <v>150</v>
@@ -8194,7 +8202,7 @@
         <v>2000</v>
       </c>
       <c r="F27" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G27" s="41" t="n">
         <v>5.6</v>
@@ -8207,7 +8215,7 @@
         <v>0.466666666666667</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K27" s="42" t="n">
         <v>0.22</v>
@@ -8253,12 +8261,12 @@
         <v>1.3884</v>
       </c>
       <c r="V27" s="45" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B28" s="47"/>
       <c r="C28" s="47"/>
@@ -8302,19 +8310,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O29" s="44" t="n">
         <f aca="false">Inputs!$B$15*Inputs!$B$7+Inputs!$B$16+Inputs!$B$34*Inputs!$B$6+Inputs!$B$35</f>
         <v>3924</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -8340,7 +8348,7 @@
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="38" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B32" s="38"/>
       <c r="C32" s="38"/>
@@ -8366,81 +8374,81 @@
     </row>
     <row r="33" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="34" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>142</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D34" s="34" t="s">
         <v>143</v>
@@ -8450,10 +8458,10 @@
         <v>2000</v>
       </c>
       <c r="F34" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G34" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H34" s="23" t="n">
         <v>48</v>
@@ -8462,7 +8470,7 @@
         <v>0.75</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K34" s="42" t="n">
         <v>0.15</v>
@@ -8507,18 +8515,18 @@
         <v>1.919</v>
       </c>
       <c r="V34" s="45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B35" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D35" s="34" t="s">
         <v>150</v>
@@ -8528,10 +8536,10 @@
         <v>2000</v>
       </c>
       <c r="F35" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G35" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H35" s="23" t="n">
         <v>60</v>
@@ -8540,7 +8548,7 @@
         <v>1.57</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K35" s="42" t="n">
         <v>0.15</v>
@@ -8585,18 +8593,18 @@
         <v>0.787400000000001</v>
       </c>
       <c r="V35" s="45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>153</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D36" s="34" t="s">
         <v>150</v>
@@ -8606,10 +8614,10 @@
         <v>2000</v>
       </c>
       <c r="F36" s="40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G36" s="50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H36" s="23" t="n">
         <v>60</v>
@@ -8618,7 +8626,7 @@
         <v>1.57</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K36" s="42" t="n">
         <v>0.15</v>
@@ -8663,12 +8671,12 @@
         <v>0.787400000000001</v>
       </c>
       <c r="V36" s="45" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B37" s="47"/>
       <c r="C37" s="47"/>
@@ -8712,14 +8720,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O38" s="44" t="n">
         <f aca="false">Inputs!$B$15*Inputs!$B$7+Inputs!$B$16</f>
         <v>1674</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -8770,17 +8778,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8791,22 +8799,22 @@
         <v>44</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H5" s="29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8814,7 +8822,7 @@
         <v>49</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C6" s="44" t="n">
         <f aca="false">N31</f>
@@ -8837,7 +8845,7 @@
         <v>1.11600833333333</v>
       </c>
       <c r="H6" s="34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8845,7 +8853,7 @@
         <v>50</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C7" s="52" t="n">
         <f aca="false">N38</f>
@@ -8868,7 +8876,7 @@
         <v>1.18178333333333</v>
       </c>
       <c r="H7" s="54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8876,7 +8884,7 @@
         <v>51</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C8" s="52" t="n">
         <f aca="false">N45</f>
@@ -8899,7 +8907,7 @@
         <v>1.15591666666667</v>
       </c>
       <c r="H8" s="54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8907,7 +8915,7 @@
         <v>52</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C9" s="44" t="n">
         <f aca="false">N52</f>
@@ -8930,7 +8938,7 @@
         <v>1.1425</v>
       </c>
       <c r="H9" s="34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8938,7 +8946,7 @@
         <v>53</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C10" s="44" t="n">
         <f aca="false">N59</f>
@@ -8961,15 +8969,15 @@
         <v>1.2148</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C11" s="44" t="n">
         <f aca="false">N66</f>
@@ -8992,7 +9000,7 @@
         <v>1.02973333333333</v>
       </c>
       <c r="H11" s="34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9000,7 +9008,7 @@
         <v>54</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C12" s="44" t="n">
         <f aca="false">N74</f>
@@ -9023,7 +9031,7 @@
         <v>1.94100833333333</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9031,7 +9039,7 @@
         <v>55</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C13" s="52" t="n">
         <f aca="false">N81</f>
@@ -9054,7 +9062,7 @@
         <v>1.54531666666667</v>
       </c>
       <c r="H13" s="54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9062,7 +9070,7 @@
         <v>56</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C14" s="52" t="n">
         <f aca="false">N88</f>
@@ -9085,7 +9093,7 @@
         <v>1.52865</v>
       </c>
       <c r="H14" s="54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9093,7 +9101,7 @@
         <v>57</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C15" s="44" t="n">
         <f aca="false">N95</f>
@@ -9116,7 +9124,7 @@
         <v>1.51523333333333</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9124,7 +9132,7 @@
         <v>58</v>
       </c>
       <c r="B16" s="34" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C16" s="44" t="n">
         <f aca="false">N102</f>
@@ -9147,15 +9155,15 @@
         <v>1.72823333333333</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C17" s="44" t="n">
         <f aca="false">N109</f>
@@ -9178,47 +9186,47 @@
         <v>1.12173333333333</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="20" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="20" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="55" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -9237,64 +9245,64 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C28" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B7</f>
         <v>4 oz</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E28" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I7+'Regular Finish – Top 3'!K7</f>
@@ -9342,17 +9350,17 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C29" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
         <v>6 oz</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E29" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
@@ -9400,17 +9408,17 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C30" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B9</f>
         <v>9 oz</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E30" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
@@ -9458,7 +9466,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B31" s="47"/>
       <c r="C31" s="47"/>
@@ -9492,7 +9500,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -9511,64 +9519,64 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N34" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C35" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B25</f>
         <v>120 ml</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E35" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
@@ -9615,17 +9623,17 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C36" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
         <v>6 oz</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E36" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
@@ -9673,17 +9681,17 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C37" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B27</f>
         <v>250–270 ml</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E37" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I27+'Regular Finish – Top 3'!K27</f>
@@ -9730,7 +9738,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B38" s="47"/>
       <c r="C38" s="47"/>
@@ -9764,7 +9772,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -9783,64 +9791,64 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C42" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B25</f>
         <v>120 ml</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E42" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
@@ -9887,17 +9895,17 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C43" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B26</f>
         <v>180–190 ml</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E43" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
@@ -9944,17 +9952,17 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C44" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
         <v>6 oz</v>
       </c>
       <c r="D44" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E44" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
@@ -10002,7 +10010,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B45" s="47"/>
       <c r="C45" s="47"/>
@@ -10036,7 +10044,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -10055,64 +10063,64 @@
     </row>
     <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C49" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B25</f>
         <v>120 ml</v>
       </c>
       <c r="D49" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E49" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
@@ -10159,17 +10167,17 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C50" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B26</f>
         <v>180–190 ml</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E50" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
@@ -10216,17 +10224,17 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C51" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B9</f>
         <v>9 oz</v>
       </c>
       <c r="D51" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E51" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
@@ -10274,7 +10282,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
@@ -10308,7 +10316,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -10327,64 +10335,64 @@
     </row>
     <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C55" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H55" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M55" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C56" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B25</f>
         <v>120 ml</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E56" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
@@ -10431,17 +10439,17 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C57" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B26</f>
         <v>180–190 ml</v>
       </c>
       <c r="D57" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E57" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
@@ -10488,17 +10496,17 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C58" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B36</f>
         <v>9 oz</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E58" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I36+'Regular Finish – Top 3'!K36</f>
@@ -10545,7 +10553,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B59" s="47"/>
       <c r="C59" s="47"/>
@@ -10579,7 +10587,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -10598,64 +10606,64 @@
     </row>
     <row r="62" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J62" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M62" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N62" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O62" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C63" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B25</f>
         <v>120 ml</v>
       </c>
       <c r="D63" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E63" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
@@ -10702,17 +10710,17 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C64" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B26</f>
         <v>180–190 ml</v>
       </c>
       <c r="D64" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E64" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
@@ -10759,17 +10767,17 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C65" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B27</f>
         <v>250–270 ml</v>
       </c>
       <c r="D65" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E65" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I27+'Regular Finish – Top 3'!K27</f>
@@ -10816,7 +10824,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B66" s="47"/>
       <c r="C66" s="47"/>
@@ -10850,12 +10858,12 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="55" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -10874,64 +10882,64 @@
     </row>
     <row r="70" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C70" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H70" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J70" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M70" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O70" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C71" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B7</f>
         <v>4 oz</v>
       </c>
       <c r="D71" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E71" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I7+'Regular Finish – Top 3'!K7</f>
@@ -10980,17 +10988,17 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C72" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
         <v>6 oz</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E72" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
@@ -11039,17 +11047,17 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C73" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B9</f>
         <v>9 oz</v>
       </c>
       <c r="D73" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E73" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
@@ -11098,7 +11106,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B74" s="47"/>
       <c r="C74" s="47"/>
@@ -11132,7 +11140,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -11151,64 +11159,64 @@
     </row>
     <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H77" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J77" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M77" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N77" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C78" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B7</f>
         <v>120 ml</v>
       </c>
       <c r="D78" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E78" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
@@ -11255,17 +11263,17 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C79" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
         <v>6 oz</v>
       </c>
       <c r="D79" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E79" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
@@ -11314,17 +11322,17 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C80" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B9</f>
         <v>250–270 ml</v>
       </c>
       <c r="D80" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E80" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I9+'Frosted Finish – Top 3'!K9</f>
@@ -11371,7 +11379,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B81" s="47"/>
       <c r="C81" s="47"/>
@@ -11405,7 +11413,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -11424,64 +11432,64 @@
     </row>
     <row r="84" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H84" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M84" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N84" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O84" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C85" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B7</f>
         <v>120 ml</v>
       </c>
       <c r="D85" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E85" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
@@ -11528,17 +11536,17 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C86" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B8</f>
         <v>180–190 ml</v>
       </c>
       <c r="D86" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E86" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
@@ -11585,17 +11593,17 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C87" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
         <v>6 oz</v>
       </c>
       <c r="D87" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E87" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
@@ -11644,7 +11652,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B88" s="47"/>
       <c r="C88" s="47"/>
@@ -11678,7 +11686,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -11697,64 +11705,64 @@
     </row>
     <row r="91" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M91" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N91" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O91" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C92" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B7</f>
         <v>120 ml</v>
       </c>
       <c r="D92" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E92" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
@@ -11801,17 +11809,17 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C93" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B8</f>
         <v>180–190 ml</v>
       </c>
       <c r="D93" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E93" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
@@ -11858,17 +11866,17 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C94" s="14" t="str">
         <f aca="false">'Regular Finish – Top 3'!B9</f>
         <v>9 oz</v>
       </c>
       <c r="D94" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E94" s="56" t="n">
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
@@ -11917,7 +11925,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B95" s="47"/>
       <c r="C95" s="47"/>
@@ -11951,7 +11959,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -11970,64 +11978,64 @@
     </row>
     <row r="98" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C98" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D98" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J98" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M98" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N98" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C99" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B7</f>
         <v>120 ml</v>
       </c>
       <c r="D99" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E99" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
@@ -12074,17 +12082,17 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C100" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B8</f>
         <v>180–190 ml</v>
       </c>
       <c r="D100" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E100" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
@@ -12131,17 +12139,17 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C101" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B36</f>
         <v>9 oz</v>
       </c>
       <c r="D101" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E101" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I36+'Frosted Finish – Top 3'!K36</f>
@@ -12189,7 +12197,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B102" s="47"/>
       <c r="C102" s="47"/>
@@ -12223,7 +12231,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -12242,64 +12250,64 @@
     </row>
     <row r="105" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>139</v>
       </c>
       <c r="D105" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M105" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N105" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O105" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C106" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B7</f>
         <v>120 ml</v>
       </c>
       <c r="D106" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E106" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
@@ -12346,17 +12354,17 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="34" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C107" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B8</f>
         <v>180–190 ml</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E107" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
@@ -12403,17 +12411,17 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="34" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C108" s="14" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B9</f>
         <v>250–270 ml</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E108" s="56" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I9+'Frosted Finish – Top 3'!K9</f>
@@ -12460,7 +12468,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="46" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B109" s="47"/>
       <c r="C109" s="47"/>
@@ -12559,809 +12567,809 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J4" s="29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="58" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D5" s="58" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E5" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F5" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G5" s="58" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H5" s="58" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="I5" s="58" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J5" s="58" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="58" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B6" s="58" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C6" s="58" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D6" s="58" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E6" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F6" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G6" s="58" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="I6" s="58" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J6" s="58" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="58" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B7" s="58" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C7" s="58" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D7" s="58" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E7" s="58" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F7" s="58" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G7" s="58" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H7" s="58" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="I7" s="58" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J7" s="58" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="58" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F20" s="58" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H20" s="58" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J20" s="58" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="58" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D21" s="58" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E21" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F21" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G21" s="58" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H21" s="58" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="I21" s="58" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J21" s="58" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="58" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D22" s="58" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E22" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F22" s="58" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H22" s="58" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I22" s="58" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J22" s="58" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="J28" s="9"/>
     </row>
@@ -13391,148 +13399,148 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="33" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="34" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="34" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="34" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="34" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="34" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="34" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="34" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="34" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="59" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="59" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="59" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B17" s="59"/>
       <c r="C17" s="59"/>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B18" s="59"/>
       <c r="C18" s="59"/>

--- a/procurement/Amber_Jar_Sourcing_Analysis.xlsx
+++ b/procurement/Amber_Jar_Sourcing_Analysis.xlsx
@@ -755,7 +755,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1713" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="766">
   <si>
     <t xml:space="preserve">FINAL RECOMMENDATION – Amber straight-sided jars &amp; launch plan</t>
   </si>
@@ -1384,7 +1384,70 @@
     <t xml:space="preserve">P3 or P4 (cheaper)</t>
   </si>
   <si>
-    <t xml:space="preserve">4. BEYOND COST</t>
+    <t xml:space="preserve">4. RANKING – cost per bottle (CAD, landed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance (per bottle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60ct (per bottle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90ct (per bottle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg per bottle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extra per bottle vs #1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current bottle (packer) – regular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1 above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current bottle (packer) – frosted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3 above</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight-sided – regular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final tab Plan B (Burch 4+6 oz + cheapest 8 oz)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight-sided – frosted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China frosted 4+6 oz + 8 oz frosted by DDP air</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Straight-sided regular rises to ~CAD 1.57/bottle if Burch's jars are US-made (50% surtax). Packer glass from TricorBraun is China-made (no surtax). Website prices + freight estimates: expect ±$0.10–0.20/bottle once quoted; the ranking is unlikely to change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. BEYOND COST</t>
   </si>
   <si>
     <t xml:space="preserve">Packer – pros</t>
@@ -1429,9 +1492,6 @@
     <t xml:space="preserve">REGULAR (glossy) – Top 3 single-source options (all three SKUs from one supplier)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jar sizes (30 / 60 / 90 ct)</t>
   </si>
   <si>
@@ -2929,31 +2989,19 @@
     <t xml:space="preserve">Action</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Owner (manufacturer)</t>
   </si>
   <si>
     <t xml:space="preserve">Confirm with your manufacturer: (a) Will they fill jars you supply? (b) Can their line handle straight-sided jars (4 / 6 / 8 oz)? (c) How do they tamper-seal glass today: induction, PS liner or shrink band? Then get their bottle + lid cost into Inputs.</t>
   </si>
   <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
     <t xml:space="preserve">Procurement</t>
   </si>
   <si>
     <t xml:space="preserve">90ct: request a quote from SKS for 500 × 8 oz amber (40530080.03S) + 760 × 70/400 induction-lined caps (2101-79B), free UPS to Ontario. Ask for COUNTRY OF ORIGIN of the jar (US-made = 50% surtax on the jar). Fallback: Uline S-24533/S-25207 (Canadian stock).</t>
   </si>
   <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
     <t xml:space="preserve">China RFQ to Qingdao Giant, Xuzhou Selead, Xuzhou Das, Chongqing Sincereal and VANJOIN: 2,000 × 120 ml + 500 × 180 ml from stock, matching style, regular AND frosted. Require 58-400 / 63-400 necks, black PP caps with induction or PS22 liners, brim-full capacity, drawings, FOB price, sample cost, lead time, carton data. Pay via Trade Assurance / secured trading.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
   </si>
   <si>
     <t xml:space="preserve">LCL door-to-door quotes from 2–3 Canadian forwarders (1.0–1.3 m³, 350–450 kg glass, to your Ontario postal code), itemized with minimums, plus one DDP-per-m³ quote.</t>
@@ -3218,7 +3266,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3383,6 +3431,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3488,14 +3548,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5920,140 +5972,140 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="61" t="s">
-        <v>721</v>
-      </c>
-      <c r="B3" s="61" t="s">
-        <v>722</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>723</v>
+      <c r="A3" s="64" t="s">
+        <v>741</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>742</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>743</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>724</v>
+        <v>217</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>725</v>
+        <v>744</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>726</v>
+        <v>745</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21" t="s">
-        <v>727</v>
+        <v>220</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>729</v>
+        <v>747</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>730</v>
+        <v>223</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>732</v>
+        <v>226</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>733</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>734</v>
+        <v>750</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>735</v>
+        <v>751</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>737</v>
+        <v>753</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>738</v>
+        <v>754</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>739</v>
+        <v>755</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>740</v>
+        <v>756</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>741</v>
+        <v>757</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>743</v>
+        <v>759</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>744</v>
+        <v>760</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>745</v>
+        <v>761</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="74" t="s">
-        <v>746</v>
-      </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="74"/>
+      <c r="A14" s="75" t="s">
+        <v>762</v>
+      </c>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="74" t="s">
-        <v>747</v>
-      </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
+      <c r="A15" s="75" t="s">
+        <v>763</v>
+      </c>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="74" t="s">
-        <v>748</v>
-      </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="74"/>
+      <c r="A16" s="75" t="s">
+        <v>764</v>
+      </c>
+      <c r="B16" s="75"/>
+      <c r="C16" s="75"/>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="74" t="s">
-        <v>749</v>
-      </c>
-      <c r="B17" s="74"/>
-      <c r="C17" s="74"/>
+      <c r="A17" s="75" t="s">
+        <v>765</v>
+      </c>
+      <c r="B17" s="75"/>
+      <c r="C17" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6077,7 +6129,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -7800,99 +7852,299 @@
       <c r="Q55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-    </row>
-    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="s">
+      <c r="D56" s="7"/>
+      <c r="E56" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="F56" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
-      <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
-    </row>
-    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="s">
+      <c r="G56" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="H56" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="6"/>
-      <c r="F58" s="6"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="6"/>
-      <c r="Q58" s="6"/>
-    </row>
-    <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="s">
+      <c r="I56" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J56" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="B59" s="6" t="s">
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
+      <c r="B57" s="37" t="s">
+        <v>218</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="D57" s="41"/>
+      <c r="E57" s="42" t="n">
+        <f aca="false">L17</f>
+        <v>1.03496474666667</v>
+      </c>
+      <c r="F57" s="42" t="n">
+        <f aca="false">L18</f>
+        <v>1.24295418666667</v>
+      </c>
+      <c r="G57" s="42" t="n">
+        <f aca="false">L19</f>
+        <v>1.52063418666667</v>
+      </c>
+      <c r="H57" s="25" t="n">
+        <f aca="false">I57/Inputs!$B$8</f>
+        <v>1.15057456</v>
+      </c>
+      <c r="I57" s="27" t="n">
+        <f aca="false">E57*Inputs!$B$5+F57*Inputs!$B$6+G57*Inputs!$B$7</f>
+        <v>3451.72368</v>
+      </c>
+      <c r="J57" s="43" t="n">
+        <f aca="false">H57-$H$57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B58" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="C58" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="D58" s="41"/>
+      <c r="E58" s="42" t="n">
+        <f aca="false">L31</f>
+        <v>1.14816</v>
+      </c>
+      <c r="F58" s="42" t="n">
+        <f aca="false">L32</f>
+        <v>1.14816</v>
+      </c>
+      <c r="G58" s="42" t="n">
+        <f aca="false">L33</f>
+        <v>2.22416</v>
+      </c>
+      <c r="H58" s="25" t="n">
+        <f aca="false">I58/Inputs!$B$8</f>
+        <v>1.32749333333333</v>
+      </c>
+      <c r="I58" s="27" t="n">
+        <f aca="false">E58*Inputs!$B$5+F58*Inputs!$B$6+G58*Inputs!$B$7</f>
+        <v>3982.48</v>
+      </c>
+      <c r="J58" s="43" t="n">
+        <f aca="false">H58-$H$57</f>
+        <v>0.176918773333333</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="B59" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="C59" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="D59" s="41"/>
+      <c r="E59" s="42" t="n">
+        <f aca="false">'Final Recommendation'!I33</f>
+        <v>1.31896666666667</v>
+      </c>
+      <c r="F59" s="42" t="n">
+        <f aca="false">'Final Recommendation'!I34</f>
+        <v>1.59012</v>
+      </c>
+      <c r="G59" s="42" t="n">
+        <f aca="false">'Final Recommendation'!K23</f>
+        <v>1.9576608</v>
+      </c>
+      <c r="H59" s="25" t="n">
+        <f aca="false">I59/Inputs!$B$8</f>
+        <v>1.47060791111111</v>
+      </c>
+      <c r="I59" s="27" t="n">
+        <f aca="false">E59*Inputs!$B$5+F59*Inputs!$B$6+G59*Inputs!$B$7</f>
+        <v>4411.82373333333</v>
+      </c>
+      <c r="J59" s="43" t="n">
+        <f aca="false">H59-$H$57</f>
+        <v>0.320033351111111</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B60" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="C60" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="D60" s="41"/>
+      <c r="E60" s="42" t="n">
+        <f aca="false">'Final Recommendation'!I41</f>
+        <v>1.41872</v>
+      </c>
+      <c r="F60" s="42" t="n">
+        <f aca="false">'Final Recommendation'!I42</f>
+        <v>1.61808</v>
+      </c>
+      <c r="G60" s="42" t="n">
+        <f aca="false">L45</f>
+        <v>2.62288</v>
+      </c>
+      <c r="H60" s="25" t="n">
+        <f aca="false">I60/Inputs!$B$8</f>
+        <v>1.65264</v>
+      </c>
+      <c r="I60" s="27" t="n">
+        <f aca="false">E60*Inputs!$B$5+F60*Inputs!$B$6+G60*Inputs!$B$7</f>
+        <v>4957.92</v>
+      </c>
+      <c r="J60" s="43" t="n">
+        <f aca="false">H60-$H$57</f>
+        <v>0.50206544</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+    </row>
+    <row r="65" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6"/>
+    </row>
+    <row r="66" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="6"/>
+    </row>
+    <row r="67" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="22">
     <mergeCell ref="A4:Q4"/>
     <mergeCell ref="A14:Q14"/>
     <mergeCell ref="A15:Q15"/>
@@ -7906,10 +8158,15 @@
     <mergeCell ref="C52:D52"/>
     <mergeCell ref="C53:D53"/>
     <mergeCell ref="A55:Q55"/>
-    <mergeCell ref="B56:Q56"/>
-    <mergeCell ref="B57:Q57"/>
-    <mergeCell ref="B58:Q58"/>
-    <mergeCell ref="B59:Q59"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="A63:Q63"/>
+    <mergeCell ref="B64:Q64"/>
+    <mergeCell ref="B65:Q65"/>
+    <mergeCell ref="B66:Q66"/>
+    <mergeCell ref="B67:Q67"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:E11">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7952,17 +8209,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -7975,19 +8232,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>221</v>
-      </c>
-      <c r="D5" s="41" t="n">
+        <v>242</v>
+      </c>
+      <c r="D5" s="44" t="n">
         <f aca="false">Inputs!$B$15</f>
         <v>3.44</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -8000,132 +8257,132 @@
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D9" s="42" t="n">
+        <v>254</v>
+      </c>
+      <c r="D9" s="45" t="n">
         <f aca="false">'Regular Finish – Top 3'!P10</f>
         <v>1.28930222222222</v>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E9" s="46" t="n">
         <f aca="false">'Regular Finish – Top 3'!S10</f>
         <v>1.64846666666667</v>
       </c>
-      <c r="F9" s="44" t="n">
+      <c r="F9" s="47" t="n">
         <f aca="false">'Regular Finish – Top 3'!Q10</f>
         <v>3867.90666666667</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D10" s="42" t="n">
+        <v>254</v>
+      </c>
+      <c r="D10" s="45" t="n">
         <f aca="false">'Regular Finish – Top 3'!P19</f>
         <v>1.38107111111111</v>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E10" s="46" t="n">
         <f aca="false">'Regular Finish – Top 3'!S19</f>
         <v>1.779</v>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="47" t="n">
         <f aca="false">'Regular Finish – Top 3'!Q19</f>
         <v>4143.21333333333</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="D11" s="42" t="n">
+        <v>264</v>
+      </c>
+      <c r="D11" s="45" t="n">
         <f aca="false">'Regular Finish – Top 3'!P28</f>
         <v>1.32866666666667</v>
       </c>
-      <c r="E11" s="43" t="n">
+      <c r="E11" s="46" t="n">
         <f aca="false">'Regular Finish – Top 3'!S28</f>
         <v>1.32866666666667</v>
       </c>
-      <c r="F11" s="44" t="n">
+      <c r="F11" s="47" t="n">
         <f aca="false">'Regular Finish – Top 3'!Q28</f>
         <v>3986</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -8138,132 +8395,132 @@
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" s="42" t="n">
+        <v>264</v>
+      </c>
+      <c r="D15" s="45" t="n">
         <f aca="false">'Frosted Finish – Top 3'!P10</f>
         <v>1.42597333333333</v>
       </c>
-      <c r="E15" s="43" t="n">
+      <c r="E15" s="46" t="n">
         <f aca="false">'Frosted Finish – Top 3'!S10</f>
         <v>1.42597333333333</v>
       </c>
-      <c r="F15" s="44" t="n">
+      <c r="F15" s="47" t="n">
         <f aca="false">'Frosted Finish – Top 3'!Q10</f>
         <v>4277.92</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" s="42" t="n">
+        <v>254</v>
+      </c>
+      <c r="D16" s="45" t="n">
         <f aca="false">'Frosted Finish – Top 3'!P19</f>
         <v>2.48930222222222</v>
       </c>
-      <c r="E16" s="43" t="n">
+      <c r="E16" s="46" t="n">
         <f aca="false">'Frosted Finish – Top 3'!S19</f>
         <v>2.84846666666667</v>
       </c>
-      <c r="F16" s="44" t="n">
+      <c r="F16" s="47" t="n">
         <f aca="false">'Frosted Finish – Top 3'!Q19</f>
         <v>7467.90666666667</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="D17" s="42" t="n">
+        <v>254</v>
+      </c>
+      <c r="D17" s="45" t="n">
         <f aca="false">'Frosted Finish – Top 3'!P28</f>
         <v>2.58107111111111</v>
       </c>
-      <c r="E17" s="43" t="n">
+      <c r="E17" s="46" t="n">
         <f aca="false">'Frosted Finish – Top 3'!S28</f>
         <v>2.979</v>
       </c>
-      <c r="F17" s="44" t="n">
+      <c r="F17" s="47" t="n">
         <f aca="false">'Frosted Finish – Top 3'!Q28</f>
         <v>7743.21333333333</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -8279,305 +8536,305 @@
         <v>87</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7" t="s">
         <v>70</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="B21" s="22" t="str">
         <f aca="false">'Split Plan – Local vs China'!B6</f>
         <v>Regular – all local (Burch; 90ct jar size guessed now)</v>
       </c>
       <c r="C21" s="22"/>
-      <c r="D21" s="45" t="n">
+      <c r="D21" s="48" t="n">
         <f aca="false">'Split Plan – Local vs China'!C6</f>
         <v>3867.90666666667</v>
       </c>
-      <c r="E21" s="46" t="n">
+      <c r="E21" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!E6</f>
         <v>4945.4</v>
       </c>
-      <c r="F21" s="46" t="n">
+      <c r="F21" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!D6</f>
         <v>0</v>
       </c>
-      <c r="G21" s="46" t="n">
+      <c r="G21" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!F6</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="B22" s="48" t="str">
+      <c r="A22" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" s="51" t="str">
         <f aca="false">'Split Plan – Local vs China'!B7</f>
         <v>Regular – FLEX: 6 oz local; 90ct is size 00 → 60ct launches</v>
       </c>
-      <c r="C22" s="48"/>
-      <c r="D22" s="49" t="n">
+      <c r="C22" s="51"/>
+      <c r="D22" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!C7</f>
         <v>4693.94</v>
       </c>
-      <c r="E22" s="49" t="n">
+      <c r="E22" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!E7</f>
         <v>4935.13</v>
       </c>
-      <c r="F22" s="49" t="n">
+      <c r="F22" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!D7</f>
         <v>826.033333333333</v>
       </c>
-      <c r="G22" s="49" t="n">
+      <c r="G22" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!F7</f>
         <v>-10.2699999999995</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="B23" s="48" t="str">
+      <c r="A23" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="B23" s="51" t="str">
         <f aca="false">'Split Plan – Local vs China'!B8</f>
         <v>Regular – FLEX: 6 oz local; 90ct is size 0 → 90ct launches</v>
       </c>
-      <c r="C23" s="48"/>
-      <c r="D23" s="49" t="n">
+      <c r="C23" s="51"/>
+      <c r="D23" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!C8</f>
         <v>4716.66</v>
       </c>
-      <c r="E23" s="49" t="n">
+      <c r="E23" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!E8</f>
         <v>4957.85</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!D8</f>
         <v>848.753333333333</v>
       </c>
-      <c r="G23" s="49" t="n">
+      <c r="G23" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!F8</f>
         <v>12.4499999999998</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="37" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="B24" s="22" t="str">
         <f aca="false">'Split Plan – Local vs China'!B9</f>
         <v>Regular – 90ct local (Burch 9 oz), rest China</v>
       </c>
       <c r="C24" s="22"/>
-      <c r="D24" s="45" t="n">
+      <c r="D24" s="48" t="n">
         <f aca="false">'Split Plan – Local vs China'!C9</f>
         <v>4576.63333333333</v>
       </c>
-      <c r="E24" s="46" t="n">
+      <c r="E24" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!E9</f>
         <v>4733.57</v>
       </c>
-      <c r="F24" s="46" t="n">
+      <c r="F24" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!D9</f>
         <v>708.726666666667</v>
       </c>
-      <c r="G24" s="46" t="n">
+      <c r="G24" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!F9</f>
         <v>-211.83</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="37" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="B25" s="22" t="str">
         <f aca="false">'Split Plan – Local vs China'!B10</f>
         <v>Regular – 90ct local (Richards, Canada), rest China</v>
       </c>
       <c r="C25" s="22"/>
-      <c r="D25" s="45" t="n">
+      <c r="D25" s="48" t="n">
         <f aca="false">'Split Plan – Local vs China'!C10</f>
         <v>4217.12</v>
       </c>
-      <c r="E25" s="46" t="n">
+      <c r="E25" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!E10</f>
         <v>4217.12</v>
       </c>
-      <c r="F25" s="46" t="n">
+      <c r="F25" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!D10</f>
         <v>349.213333333332</v>
       </c>
-      <c r="G25" s="46" t="n">
+      <c r="G25" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!F10</f>
         <v>-728.280000000001</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="37" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="B26" s="22" t="str">
         <f aca="false">'Split Plan – Local vs China'!B12</f>
         <v>Frosted – all local (Burch + spray frost)</v>
       </c>
       <c r="C26" s="22"/>
-      <c r="D26" s="45" t="n">
+      <c r="D26" s="48" t="n">
         <f aca="false">'Split Plan – Local vs China'!C12</f>
         <v>7467.90666666667</v>
       </c>
-      <c r="E26" s="46" t="n">
+      <c r="E26" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!E12</f>
         <v>8545.4</v>
       </c>
-      <c r="F26" s="46" t="n">
+      <c r="F26" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!D12</f>
         <v>0</v>
       </c>
-      <c r="G26" s="46" t="n">
+      <c r="G26" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!F12</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="B27" s="48" t="str">
+      <c r="A27" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="B27" s="51" t="str">
         <f aca="false">'Split Plan – Local vs China'!B13</f>
         <v>Frosted – FLEX: 6 oz local; 90ct is size 00 → 60ct launches</v>
       </c>
-      <c r="C27" s="48"/>
-      <c r="D27" s="49" t="n">
+      <c r="C27" s="51"/>
+      <c r="D27" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!C13</f>
         <v>6075.42</v>
       </c>
-      <c r="E27" s="49" t="n">
+      <c r="E27" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!E13</f>
         <v>6316.61</v>
       </c>
-      <c r="F27" s="49" t="n">
+      <c r="F27" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!D13</f>
         <v>-1392.48666666667</v>
       </c>
-      <c r="G27" s="49" t="n">
+      <c r="G27" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!F13</f>
         <v>-2228.79</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="B28" s="48" t="str">
+      <c r="A28" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="B28" s="51" t="str">
         <f aca="false">'Split Plan – Local vs China'!B14</f>
         <v>Frosted – FLEX: 6 oz local; 90ct is size 0 → 90ct launches</v>
       </c>
-      <c r="C28" s="48"/>
-      <c r="D28" s="49" t="n">
+      <c r="C28" s="51"/>
+      <c r="D28" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!C14</f>
         <v>6091.02</v>
       </c>
-      <c r="E28" s="49" t="n">
+      <c r="E28" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!E14</f>
         <v>6332.21</v>
       </c>
-      <c r="F28" s="49" t="n">
+      <c r="F28" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!D14</f>
         <v>-1376.88666666667</v>
       </c>
-      <c r="G28" s="49" t="n">
+      <c r="G28" s="52" t="n">
         <f aca="false">'Split Plan – Local vs China'!F14</f>
         <v>-2213.19</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="37" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="B29" s="22" t="str">
         <f aca="false">'Split Plan – Local vs China'!B15</f>
         <v>Frosted – 90ct local (Burch 9 oz + spray frost), rest China</v>
       </c>
       <c r="C29" s="22"/>
-      <c r="D29" s="45" t="n">
+      <c r="D29" s="48" t="n">
         <f aca="false">'Split Plan – Local vs China'!C15</f>
         <v>5950.99333333333</v>
       </c>
-      <c r="E29" s="46" t="n">
+      <c r="E29" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!E15</f>
         <v>6107.93</v>
       </c>
-      <c r="F29" s="46" t="n">
+      <c r="F29" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!D15</f>
         <v>-1516.91333333333</v>
       </c>
-      <c r="G29" s="46" t="n">
+      <c r="G29" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!F15</f>
         <v>-2437.47</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="37" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B30" s="22" t="str">
         <f aca="false">'Split Plan – Local vs China'!B16</f>
         <v>Frosted – 90ct local (Liquid Bottles stock), rest China</v>
       </c>
       <c r="C30" s="22"/>
-      <c r="D30" s="45" t="n">
+      <c r="D30" s="48" t="n">
         <f aca="false">'Split Plan – Local vs China'!C16</f>
         <v>5679.64</v>
       </c>
-      <c r="E30" s="46" t="n">
+      <c r="E30" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!E16</f>
         <v>6238.56</v>
       </c>
-      <c r="F30" s="46" t="n">
+      <c r="F30" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!D16</f>
         <v>-1788.26666666667</v>
       </c>
-      <c r="G30" s="46" t="n">
+      <c r="G30" s="49" t="n">
         <f aca="false">'Split Plan – Local vs China'!F16</f>
         <v>-2306.84</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>274</v>
+        <v>294</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="36" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="36" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="36" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -8622,335 +8879,335 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="36" t="s">
-        <v>282</v>
-      </c>
-      <c r="B5" s="50" t="n">
+        <v>302</v>
+      </c>
+      <c r="B5" s="53" t="n">
         <v>2000</v>
       </c>
-      <c r="C5" s="51" t="s">
-        <v>283</v>
+      <c r="C5" s="54" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="B6" s="50" t="n">
+        <v>304</v>
+      </c>
+      <c r="B6" s="53" t="n">
         <v>500</v>
       </c>
-      <c r="C6" s="51" t="s">
-        <v>285</v>
+      <c r="C6" s="54" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="36" t="s">
-        <v>286</v>
-      </c>
-      <c r="B7" s="50" t="n">
+        <v>306</v>
+      </c>
+      <c r="B7" s="53" t="n">
         <v>500</v>
       </c>
-      <c r="C7" s="51" t="s">
-        <v>285</v>
+      <c r="C7" s="54" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="36" t="s">
-        <v>287</v>
-      </c>
-      <c r="B8" s="52" t="n">
+        <v>307</v>
+      </c>
+      <c r="B8" s="55" t="n">
         <f aca="false">$B$5+$B$6+$B$7</f>
         <v>3000</v>
       </c>
-      <c r="C8" s="51" t="s">
-        <v>288</v>
+      <c r="C8" s="54" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="53" t="n">
+        <v>309</v>
+      </c>
+      <c r="B9" s="56" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="51" t="s">
-        <v>290</v>
+      <c r="C9" s="54" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B10" s="40" t="n">
         <v>1.424</v>
       </c>
-      <c r="C10" s="51" t="s">
-        <v>292</v>
+      <c r="C10" s="54" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="54" t="n">
+        <v>313</v>
+      </c>
+      <c r="B11" s="57" t="n">
         <v>3.74</v>
       </c>
-      <c r="C11" s="51" t="s">
-        <v>294</v>
+      <c r="C11" s="54" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36" t="s">
-        <v>295</v>
-      </c>
-      <c r="B12" s="54" t="n">
+        <v>315</v>
+      </c>
+      <c r="B12" s="57" t="n">
         <v>0.3</v>
       </c>
-      <c r="C12" s="51" t="s">
-        <v>296</v>
+      <c r="C12" s="54" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="36" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">$B$11-$B$12</f>
         <v>3.44</v>
       </c>
-      <c r="C13" s="51" t="s">
-        <v>298</v>
+      <c r="C13" s="54" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="36" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="51" t="s">
-        <v>300</v>
+        <v>319</v>
+      </c>
+      <c r="B14" s="57"/>
+      <c r="C14" s="54" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="36" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">IF($B$14="",$B$13,$B$14)</f>
         <v>3.44</v>
       </c>
-      <c r="C15" s="51" t="s">
-        <v>302</v>
+      <c r="C15" s="54" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="17" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="36" t="s">
-        <v>304</v>
-      </c>
-      <c r="B18" s="55" t="n">
+        <v>324</v>
+      </c>
+      <c r="B18" s="58" t="n">
         <v>650</v>
       </c>
-      <c r="C18" s="51" t="s">
-        <v>305</v>
+      <c r="C18" s="54" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36" t="s">
-        <v>306</v>
-      </c>
-      <c r="B19" s="55" t="n">
+        <v>326</v>
+      </c>
+      <c r="B19" s="58" t="n">
         <v>175</v>
       </c>
-      <c r="C19" s="51" t="s">
-        <v>307</v>
+      <c r="C19" s="54" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="s">
-        <v>308</v>
-      </c>
-      <c r="B20" s="55" t="n">
+        <v>328</v>
+      </c>
+      <c r="B20" s="58" t="n">
         <v>300</v>
       </c>
-      <c r="C20" s="51" t="s">
-        <v>309</v>
+      <c r="C20" s="54" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="s">
-        <v>310</v>
-      </c>
-      <c r="B21" s="55" t="n">
+        <v>330</v>
+      </c>
+      <c r="B21" s="58" t="n">
         <v>1250</v>
       </c>
-      <c r="C21" s="51" t="s">
-        <v>311</v>
+      <c r="C21" s="54" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="36" t="s">
-        <v>313</v>
-      </c>
-      <c r="B24" s="55" t="n">
+        <v>333</v>
+      </c>
+      <c r="B24" s="58" t="n">
         <v>400</v>
       </c>
-      <c r="C24" s="51" t="s">
-        <v>314</v>
+      <c r="C24" s="54" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="36" t="s">
-        <v>315</v>
-      </c>
-      <c r="B25" s="55" t="n">
+        <v>335</v>
+      </c>
+      <c r="B25" s="58" t="n">
         <v>125</v>
       </c>
-      <c r="C25" s="51" t="s">
-        <v>316</v>
+      <c r="C25" s="54" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="36" t="s">
-        <v>317</v>
-      </c>
-      <c r="B26" s="55" t="n">
+        <v>337</v>
+      </c>
+      <c r="B26" s="58" t="n">
         <v>150</v>
       </c>
-      <c r="C26" s="51" t="s">
-        <v>318</v>
+      <c r="C26" s="54" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="36" t="s">
-        <v>319</v>
-      </c>
-      <c r="B27" s="55" t="n">
+        <v>339</v>
+      </c>
+      <c r="B27" s="58" t="n">
         <v>1080</v>
       </c>
-      <c r="C27" s="51" t="s">
-        <v>320</v>
+      <c r="C27" s="54" t="s">
+        <v>340</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="36" t="s">
-        <v>321</v>
-      </c>
-      <c r="B28" s="55" t="n">
+        <v>341</v>
+      </c>
+      <c r="B28" s="58" t="n">
         <v>1060</v>
       </c>
-      <c r="C28" s="51" t="s">
-        <v>322</v>
+      <c r="C28" s="54" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="36" t="s">
-        <v>323</v>
-      </c>
-      <c r="B29" s="55" t="n">
+        <v>343</v>
+      </c>
+      <c r="B29" s="58" t="n">
         <v>870</v>
       </c>
-      <c r="C29" s="51" t="s">
-        <v>324</v>
+      <c r="C29" s="54" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="36" t="s">
-        <v>325</v>
-      </c>
-      <c r="B30" s="55" t="n">
+        <v>345</v>
+      </c>
+      <c r="B30" s="58" t="n">
         <v>600</v>
       </c>
-      <c r="C30" s="51" t="s">
-        <v>326</v>
+      <c r="C30" s="54" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>327</v>
+        <v>347</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="36" t="s">
-        <v>328</v>
-      </c>
-      <c r="B33" s="56" t="n">
+        <v>348</v>
+      </c>
+      <c r="B33" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="51" t="s">
-        <v>329</v>
+      <c r="C33" s="54" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="36" t="s">
-        <v>330</v>
-      </c>
-      <c r="B34" s="56" t="n">
+        <v>350</v>
+      </c>
+      <c r="B34" s="59" t="n">
         <v>0.5</v>
       </c>
-      <c r="C34" s="51" t="s">
-        <v>331</v>
+      <c r="C34" s="54" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="36" t="s">
-        <v>333</v>
-      </c>
-      <c r="B37" s="54" t="n">
+        <v>353</v>
+      </c>
+      <c r="B37" s="57" t="n">
         <v>0.45</v>
       </c>
-      <c r="C37" s="51" t="s">
-        <v>334</v>
+      <c r="C37" s="54" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="36" t="s">
-        <v>335</v>
-      </c>
-      <c r="B38" s="55" t="n">
+        <v>355</v>
+      </c>
+      <c r="B38" s="58" t="n">
         <v>650</v>
       </c>
-      <c r="C38" s="51" t="s">
-        <v>336</v>
+      <c r="C38" s="54" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="36" t="s">
-        <v>337</v>
-      </c>
-      <c r="B39" s="55" t="n">
+        <v>357</v>
+      </c>
+      <c r="B39" s="58" t="n">
         <v>300</v>
       </c>
-      <c r="C39" s="51" t="s">
-        <v>338</v>
+      <c r="C39" s="54" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -8978,295 +9235,295 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>340</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>341</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="B5" s="57" t="s">
-        <v>343</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>345</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>346</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>347</v>
+      <c r="A5" s="60" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" s="60" t="s">
+        <v>363</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>364</v>
+      </c>
+      <c r="D5" s="60" t="s">
+        <v>365</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>366</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="B6" s="58" t="n">
+        <v>368</v>
+      </c>
+      <c r="B6" s="61" t="n">
         <v>21.7</v>
       </c>
-      <c r="C6" s="59" t="n">
+      <c r="C6" s="62" t="n">
         <v>7.65</v>
       </c>
       <c r="D6" s="39" t="n">
         <f aca="false">(PI()*(C6/2)^2*(B6-C6)+4/3*PI()*(C6/2)^3)/1000</f>
         <v>0.88020033593373</v>
       </c>
-      <c r="E6" s="60" t="n">
+      <c r="E6" s="63" t="n">
         <f aca="false">D6/$B$10</f>
         <v>1.60036424715224</v>
       </c>
-      <c r="F6" s="60" t="n">
+      <c r="F6" s="63" t="n">
         <f aca="false">E6*(1+$B$11)</f>
         <v>1.84041888422507</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
-        <v>349</v>
-      </c>
-      <c r="B7" s="58" t="n">
+        <v>369</v>
+      </c>
+      <c r="B7" s="61" t="n">
         <v>23.3</v>
       </c>
-      <c r="C7" s="59" t="n">
+      <c r="C7" s="62" t="n">
         <v>8.53</v>
       </c>
       <c r="D7" s="39" t="n">
         <f aca="false">(PI()*(C7/2)^2*(B7-C7)+4/3*PI()*(C7/2)^3)/1000</f>
         <v>1.16902234447664</v>
       </c>
-      <c r="E7" s="60" t="n">
+      <c r="E7" s="63" t="n">
         <f aca="false">D7/$B$10</f>
         <v>2.1254951717757</v>
       </c>
-      <c r="F7" s="60" t="n">
+      <c r="F7" s="63" t="n">
         <f aca="false">E7*(1+$B$11)</f>
         <v>2.44431944754206</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="36" t="s">
-        <v>351</v>
-      </c>
-      <c r="B10" s="59" t="n">
+        <v>371</v>
+      </c>
+      <c r="B10" s="62" t="n">
         <v>0.55</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="36" t="s">
-        <v>353</v>
-      </c>
-      <c r="B11" s="56" t="n">
+        <v>373</v>
+      </c>
+      <c r="B11" s="59" t="n">
         <v>0.15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="36" t="s">
-        <v>355</v>
-      </c>
-      <c r="B12" s="56" t="n">
+        <v>375</v>
+      </c>
+      <c r="B12" s="59" t="n">
         <v>0.5</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>356</v>
+        <v>376</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="36" t="s">
-        <v>357</v>
-      </c>
-      <c r="B13" s="56" t="n">
+        <v>377</v>
+      </c>
+      <c r="B13" s="59" t="n">
         <v>0.9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="17" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="61" t="s">
-        <v>359</v>
-      </c>
-      <c r="C16" s="61" t="s">
-        <v>360</v>
+      <c r="B16" s="64" t="s">
+        <v>379</v>
+      </c>
+      <c r="C16" s="64" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>361</v>
-      </c>
-      <c r="B17" s="53" t="n">
+        <v>381</v>
+      </c>
+      <c r="B17" s="56" t="n">
         <v>118</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="B18" s="53" t="n">
+        <v>384</v>
+      </c>
+      <c r="B18" s="56" t="n">
         <v>177</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="37" t="s">
-        <v>366</v>
-      </c>
-      <c r="B19" s="53" t="n">
+        <v>386</v>
+      </c>
+      <c r="B19" s="56" t="n">
         <v>190</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="B20" s="53" t="n">
+        <v>388</v>
+      </c>
+      <c r="B20" s="56" t="n">
         <v>237</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="37" t="s">
-        <v>370</v>
-      </c>
-      <c r="B21" s="53" t="n">
+        <v>390</v>
+      </c>
+      <c r="B21" s="56" t="n">
         <v>250</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="37" t="s">
-        <v>372</v>
-      </c>
-      <c r="B22" s="53" t="n">
+        <v>392</v>
+      </c>
+      <c r="B22" s="56" t="n">
         <v>266</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="C25" s="57" t="s">
-        <v>374</v>
-      </c>
-      <c r="D25" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="E25" s="57" t="s">
-        <v>376</v>
-      </c>
-      <c r="F25" s="57" t="s">
-        <v>361</v>
-      </c>
-      <c r="G25" s="57" t="s">
-        <v>364</v>
-      </c>
-      <c r="H25" s="57" t="s">
-        <v>366</v>
-      </c>
-      <c r="I25" s="57" t="s">
-        <v>368</v>
-      </c>
-      <c r="J25" s="57" t="s">
-        <v>370</v>
-      </c>
-      <c r="K25" s="57" t="s">
-        <v>372</v>
+      <c r="B25" s="60" t="s">
+        <v>362</v>
+      </c>
+      <c r="C25" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D25" s="60" t="s">
+        <v>395</v>
+      </c>
+      <c r="E25" s="60" t="s">
+        <v>396</v>
+      </c>
+      <c r="F25" s="60" t="s">
+        <v>381</v>
+      </c>
+      <c r="G25" s="60" t="s">
+        <v>384</v>
+      </c>
+      <c r="H25" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="I25" s="60" t="s">
+        <v>388</v>
+      </c>
+      <c r="J25" s="60" t="s">
+        <v>390</v>
+      </c>
+      <c r="K25" s="60" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="62" t="s">
-        <v>348</v>
-      </c>
-      <c r="C26" s="53" t="n">
+      <c r="B26" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="C26" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="D26" s="63" t="n">
+      <c r="D26" s="66" t="n">
         <f aca="false">C26*INDEX($E$6:$E$7,MATCH(B26,$A$6:$A$7,0))</f>
         <v>48.0109274145671</v>
       </c>
-      <c r="E26" s="63" t="n">
+      <c r="E26" s="66" t="n">
         <f aca="false">C26*INDEX($F$6:$F$7,MATCH(B26,$A$6:$A$7,0))</f>
         <v>55.2125665267522</v>
       </c>
-      <c r="F26" s="64" t="n">
+      <c r="F26" s="67" t="n">
         <f aca="false">$D26/$B$17</f>
         <v>0.406872266225145</v>
       </c>
-      <c r="G26" s="64" t="n">
+      <c r="G26" s="67" t="n">
         <f aca="false">$D26/$B$18</f>
         <v>0.27124817748343</v>
       </c>
-      <c r="H26" s="64" t="n">
+      <c r="H26" s="67" t="n">
         <f aca="false">$D26/$B$19</f>
         <v>0.252689091655616</v>
       </c>
-      <c r="I26" s="64" t="n">
+      <c r="I26" s="67" t="n">
         <f aca="false">$D26/$B$20</f>
         <v>0.202577752804081</v>
       </c>
-      <c r="J26" s="64" t="n">
+      <c r="J26" s="67" t="n">
         <f aca="false">$D26/$B$21</f>
         <v>0.192043709658268</v>
       </c>
-      <c r="K26" s="64" t="n">
+      <c r="K26" s="67" t="n">
         <f aca="false">$D26/$B$22</f>
         <v>0.18049220832544</v>
       </c>
@@ -9275,41 +9532,41 @@
       <c r="A27" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B27" s="62" t="s">
-        <v>349</v>
-      </c>
-      <c r="C27" s="53" t="n">
+      <c r="B27" s="65" t="s">
+        <v>369</v>
+      </c>
+      <c r="C27" s="56" t="n">
         <v>60</v>
       </c>
-      <c r="D27" s="63" t="n">
+      <c r="D27" s="66" t="n">
         <f aca="false">C27*INDEX($E$6:$E$7,MATCH(B27,$A$6:$A$7,0))</f>
         <v>127.529710306542</v>
       </c>
-      <c r="E27" s="63" t="n">
+      <c r="E27" s="66" t="n">
         <f aca="false">C27*INDEX($F$6:$F$7,MATCH(B27,$A$6:$A$7,0))</f>
         <v>146.659166852524</v>
       </c>
-      <c r="F27" s="64" t="n">
+      <c r="F27" s="67" t="n">
         <f aca="false">$D27/$B$17</f>
         <v>1.0807602568351</v>
       </c>
-      <c r="G27" s="64" t="n">
+      <c r="G27" s="67" t="n">
         <f aca="false">$D27/$B$18</f>
         <v>0.720506837890069</v>
       </c>
-      <c r="H27" s="64" t="n">
+      <c r="H27" s="67" t="n">
         <f aca="false">$D27/$B$19</f>
         <v>0.67120900161338</v>
       </c>
-      <c r="I27" s="64" t="n">
+      <c r="I27" s="67" t="n">
         <f aca="false">$D27/$B$20</f>
         <v>0.53810004348752</v>
       </c>
-      <c r="J27" s="64" t="n">
+      <c r="J27" s="67" t="n">
         <f aca="false">$D27/$B$21</f>
         <v>0.510118841226169</v>
       </c>
-      <c r="K27" s="64" t="n">
+      <c r="K27" s="67" t="n">
         <f aca="false">$D27/$B$22</f>
         <v>0.479435001152415</v>
       </c>
@@ -9318,41 +9575,41 @@
       <c r="A28" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B28" s="62" t="s">
-        <v>348</v>
-      </c>
-      <c r="C28" s="53" t="n">
+      <c r="B28" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="C28" s="56" t="n">
         <v>60</v>
       </c>
-      <c r="D28" s="63" t="n">
+      <c r="D28" s="66" t="n">
         <f aca="false">C28*INDEX($E$6:$E$7,MATCH(B28,$A$6:$A$7,0))</f>
         <v>96.0218548291342</v>
       </c>
-      <c r="E28" s="63" t="n">
+      <c r="E28" s="66" t="n">
         <f aca="false">C28*INDEX($F$6:$F$7,MATCH(B28,$A$6:$A$7,0))</f>
         <v>110.425133053504</v>
       </c>
-      <c r="F28" s="64" t="n">
+      <c r="F28" s="67" t="n">
         <f aca="false">$D28/$B$17</f>
         <v>0.81374453245029</v>
       </c>
-      <c r="G28" s="64" t="n">
+      <c r="G28" s="67" t="n">
         <f aca="false">$D28/$B$18</f>
         <v>0.54249635496686</v>
       </c>
-      <c r="H28" s="64" t="n">
+      <c r="H28" s="67" t="n">
         <f aca="false">$D28/$B$19</f>
         <v>0.505378183311233</v>
       </c>
-      <c r="I28" s="64" t="n">
+      <c r="I28" s="67" t="n">
         <f aca="false">$D28/$B$20</f>
         <v>0.405155505608161</v>
       </c>
-      <c r="J28" s="64" t="n">
+      <c r="J28" s="67" t="n">
         <f aca="false">$D28/$B$21</f>
         <v>0.384087419316537</v>
       </c>
-      <c r="K28" s="64" t="n">
+      <c r="K28" s="67" t="n">
         <f aca="false">$D28/$B$22</f>
         <v>0.360984416650881</v>
       </c>
@@ -9361,41 +9618,41 @@
       <c r="A29" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="62" t="s">
-        <v>349</v>
-      </c>
-      <c r="C29" s="53" t="n">
+      <c r="B29" s="65" t="s">
+        <v>369</v>
+      </c>
+      <c r="C29" s="56" t="n">
         <v>90</v>
       </c>
-      <c r="D29" s="63" t="n">
+      <c r="D29" s="66" t="n">
         <f aca="false">C29*INDEX($E$6:$E$7,MATCH(B29,$A$6:$A$7,0))</f>
         <v>191.294565459813</v>
       </c>
-      <c r="E29" s="63" t="n">
+      <c r="E29" s="66" t="n">
         <f aca="false">C29*INDEX($F$6:$F$7,MATCH(B29,$A$6:$A$7,0))</f>
         <v>219.988750278785</v>
       </c>
-      <c r="F29" s="64" t="n">
+      <c r="F29" s="67" t="n">
         <f aca="false">$D29/$B$17</f>
         <v>1.62114038525266</v>
       </c>
-      <c r="G29" s="64" t="n">
+      <c r="G29" s="67" t="n">
         <f aca="false">$D29/$B$18</f>
         <v>1.0807602568351</v>
       </c>
-      <c r="H29" s="64" t="n">
+      <c r="H29" s="67" t="n">
         <f aca="false">$D29/$B$19</f>
         <v>1.00681350242007</v>
       </c>
-      <c r="I29" s="64" t="n">
+      <c r="I29" s="67" t="n">
         <f aca="false">$D29/$B$20</f>
         <v>0.80715006523128</v>
       </c>
-      <c r="J29" s="64" t="n">
+      <c r="J29" s="67" t="n">
         <f aca="false">$D29/$B$21</f>
         <v>0.765178261839254</v>
       </c>
-      <c r="K29" s="64" t="n">
+      <c r="K29" s="67" t="n">
         <f aca="false">$D29/$B$22</f>
         <v>0.719152501728622</v>
       </c>
@@ -9404,100 +9661,100 @@
       <c r="A30" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="B30" s="62" t="s">
-        <v>348</v>
-      </c>
-      <c r="C30" s="53" t="n">
+      <c r="B30" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="56" t="n">
         <v>90</v>
       </c>
-      <c r="D30" s="63" t="n">
+      <c r="D30" s="66" t="n">
         <f aca="false">C30*INDEX($E$6:$E$7,MATCH(B30,$A$6:$A$7,0))</f>
         <v>144.032782243701</v>
       </c>
-      <c r="E30" s="63" t="n">
+      <c r="E30" s="66" t="n">
         <f aca="false">C30*INDEX($F$6:$F$7,MATCH(B30,$A$6:$A$7,0))</f>
         <v>165.637699580256</v>
       </c>
-      <c r="F30" s="64" t="n">
+      <c r="F30" s="67" t="n">
         <f aca="false">$D30/$B$17</f>
         <v>1.22061679867543</v>
       </c>
-      <c r="G30" s="64" t="n">
+      <c r="G30" s="67" t="n">
         <f aca="false">$D30/$B$18</f>
         <v>0.81374453245029</v>
       </c>
-      <c r="H30" s="64" t="n">
+      <c r="H30" s="67" t="n">
         <f aca="false">$D30/$B$19</f>
         <v>0.758067274966849</v>
       </c>
-      <c r="I30" s="64" t="n">
+      <c r="I30" s="67" t="n">
         <f aca="false">$D30/$B$20</f>
         <v>0.607733258412242</v>
       </c>
-      <c r="J30" s="64" t="n">
+      <c r="J30" s="67" t="n">
         <f aca="false">$D30/$B$21</f>
         <v>0.576131128974805</v>
       </c>
-      <c r="K30" s="64" t="n">
+      <c r="K30" s="67" t="n">
         <f aca="false">$D30/$B$22</f>
         <v>0.541476624976321</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="57" t="s">
+      <c r="A33" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="57" t="s">
-        <v>342</v>
-      </c>
-      <c r="C33" s="57" t="s">
-        <v>374</v>
-      </c>
-      <c r="D33" s="57" t="s">
-        <v>375</v>
-      </c>
-      <c r="E33" s="57" t="s">
-        <v>376</v>
-      </c>
-      <c r="F33" s="57" t="s">
-        <v>361</v>
-      </c>
-      <c r="G33" s="57" t="s">
-        <v>364</v>
-      </c>
-      <c r="H33" s="57" t="s">
-        <v>366</v>
-      </c>
-      <c r="I33" s="57" t="s">
-        <v>368</v>
-      </c>
-      <c r="J33" s="57" t="s">
-        <v>370</v>
-      </c>
-      <c r="K33" s="57" t="s">
-        <v>372</v>
+      <c r="B33" s="60" t="s">
+        <v>362</v>
+      </c>
+      <c r="C33" s="60" t="s">
+        <v>394</v>
+      </c>
+      <c r="D33" s="60" t="s">
+        <v>395</v>
+      </c>
+      <c r="E33" s="60" t="s">
+        <v>396</v>
+      </c>
+      <c r="F33" s="60" t="s">
+        <v>381</v>
+      </c>
+      <c r="G33" s="60" t="s">
+        <v>384</v>
+      </c>
+      <c r="H33" s="60" t="s">
+        <v>386</v>
+      </c>
+      <c r="I33" s="60" t="s">
+        <v>388</v>
+      </c>
+      <c r="J33" s="60" t="s">
+        <v>390</v>
+      </c>
+      <c r="K33" s="60" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="62" t="s">
-        <v>348</v>
-      </c>
-      <c r="C34" s="53" t="n">
+      <c r="B34" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="C34" s="56" t="n">
         <v>30</v>
       </c>
-      <c r="D34" s="63" t="n">
+      <c r="D34" s="66" t="n">
         <f aca="false">C34*INDEX($E$6:$E$7,MATCH(B34,$A$6:$A$7,0))</f>
         <v>48.0109274145671</v>
       </c>
-      <c r="E34" s="63" t="n">
+      <c r="E34" s="66" t="n">
         <f aca="false">C34*INDEX($F$6:$F$7,MATCH(B34,$A$6:$A$7,0))</f>
         <v>55.2125665267522</v>
       </c>
@@ -9530,17 +9787,17 @@
       <c r="A35" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="62" t="s">
-        <v>349</v>
-      </c>
-      <c r="C35" s="53" t="n">
+      <c r="B35" s="65" t="s">
+        <v>369</v>
+      </c>
+      <c r="C35" s="56" t="n">
         <v>60</v>
       </c>
-      <c r="D35" s="63" t="n">
+      <c r="D35" s="66" t="n">
         <f aca="false">C35*INDEX($E$6:$E$7,MATCH(B35,$A$6:$A$7,0))</f>
         <v>127.529710306542</v>
       </c>
-      <c r="E35" s="63" t="n">
+      <c r="E35" s="66" t="n">
         <f aca="false">C35*INDEX($F$6:$F$7,MATCH(B35,$A$6:$A$7,0))</f>
         <v>146.659166852524</v>
       </c>
@@ -9573,17 +9830,17 @@
       <c r="A36" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="B36" s="62" t="s">
-        <v>348</v>
-      </c>
-      <c r="C36" s="53" t="n">
+      <c r="B36" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="C36" s="56" t="n">
         <v>60</v>
       </c>
-      <c r="D36" s="63" t="n">
+      <c r="D36" s="66" t="n">
         <f aca="false">C36*INDEX($E$6:$E$7,MATCH(B36,$A$6:$A$7,0))</f>
         <v>96.0218548291342</v>
       </c>
-      <c r="E36" s="63" t="n">
+      <c r="E36" s="66" t="n">
         <f aca="false">C36*INDEX($F$6:$F$7,MATCH(B36,$A$6:$A$7,0))</f>
         <v>110.425133053504</v>
       </c>
@@ -9616,17 +9873,17 @@
       <c r="A37" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="B37" s="62" t="s">
-        <v>349</v>
-      </c>
-      <c r="C37" s="53" t="n">
+      <c r="B37" s="65" t="s">
+        <v>369</v>
+      </c>
+      <c r="C37" s="56" t="n">
         <v>90</v>
       </c>
-      <c r="D37" s="63" t="n">
+      <c r="D37" s="66" t="n">
         <f aca="false">C37*INDEX($E$6:$E$7,MATCH(B37,$A$6:$A$7,0))</f>
         <v>191.294565459813</v>
       </c>
-      <c r="E37" s="63" t="n">
+      <c r="E37" s="66" t="n">
         <f aca="false">C37*INDEX($F$6:$F$7,MATCH(B37,$A$6:$A$7,0))</f>
         <v>219.988750278785</v>
       </c>
@@ -9659,17 +9916,17 @@
       <c r="A38" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="B38" s="62" t="s">
-        <v>348</v>
-      </c>
-      <c r="C38" s="53" t="n">
+      <c r="B38" s="65" t="s">
+        <v>368</v>
+      </c>
+      <c r="C38" s="56" t="n">
         <v>90</v>
       </c>
-      <c r="D38" s="63" t="n">
+      <c r="D38" s="66" t="n">
         <f aca="false">C38*INDEX($E$6:$E$7,MATCH(B38,$A$6:$A$7,0))</f>
         <v>144.032782243701</v>
       </c>
-      <c r="E38" s="63" t="n">
+      <c r="E38" s="66" t="n">
         <f aca="false">C38*INDEX($F$6:$F$7,MATCH(B38,$A$6:$A$7,0))</f>
         <v>165.637699580256</v>
       </c>
@@ -9700,42 +9957,42 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="36" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="36" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="36" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="36" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="36" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="36" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="36" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -9799,17 +10056,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -9834,43 +10091,43 @@
       <c r="V4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="65" t="s">
-        <v>389</v>
-      </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
+      <c r="A5" s="68" t="s">
+        <v>409</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>69</v>
@@ -9879,66 +10136,66 @@
         <v>20</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E7" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -9947,10 +10204,10 @@
       <c r="F7" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="66" t="n">
+      <c r="G7" s="69" t="n">
         <v>11.45</v>
       </c>
-      <c r="H7" s="53" t="n">
+      <c r="H7" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I7" s="39" t="n">
@@ -9958,12 +10215,12 @@
         <v>0.477083333333333</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="K7" s="40" t="n">
         <v>0.14</v>
       </c>
-      <c r="L7" s="60" t="n">
+      <c r="L7" s="63" t="n">
         <f aca="false">IF(F7="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10003,21 +10260,21 @@
         <v>2.19440666666667</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="E8" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -10026,10 +10283,10 @@
       <c r="F8" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="66" t="n">
+      <c r="G8" s="69" t="n">
         <v>8.13</v>
       </c>
-      <c r="H8" s="53" t="n">
+      <c r="H8" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I8" s="39" t="n">
@@ -10037,12 +10294,12 @@
         <v>0.6775</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="K8" s="40" t="n">
         <v>0.13</v>
       </c>
-      <c r="L8" s="60" t="n">
+      <c r="L8" s="63" t="n">
         <f aca="false">IF(F8="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10082,21 +10339,21 @@
         <v>1.92325333333333</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E9" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -10105,10 +10362,10 @@
       <c r="F9" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="66" t="n">
+      <c r="G9" s="69" t="n">
         <v>5.29</v>
       </c>
-      <c r="H9" s="53" t="n">
+      <c r="H9" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I9" s="39" t="n">
@@ -10116,12 +10373,12 @@
         <v>0.440833333333333</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="K9" s="40" t="n">
         <v>0.17</v>
       </c>
-      <c r="L9" s="60" t="n">
+      <c r="L9" s="63" t="n">
         <f aca="false">IF(F9="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10161,17 +10418,17 @@
         <v>2.20330666666667</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
       <c r="D10" s="29"/>
-      <c r="E10" s="67" t="n">
+      <c r="E10" s="70" t="n">
         <f aca="false">SUM(E7:E9)</f>
         <v>3000</v>
       </c>
@@ -10210,19 +10467,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O11" s="27" t="n">
         <f aca="false">Inputs!$B$18*Inputs!$B$10+Inputs!$B$19</f>
         <v>1100.6</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>423</v>
+        <v>443</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -10247,43 +10504,43 @@
       <c r="V13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="65" t="s">
-        <v>424</v>
-      </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
-      <c r="V14" s="65"/>
+      <c r="A14" s="68" t="s">
+        <v>444</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="68"/>
     </row>
     <row r="15" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>69</v>
@@ -10292,66 +10549,66 @@
         <v>20</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P15" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E16" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -10360,10 +10617,10 @@
       <c r="F16" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="69" t="n">
         <v>12.95</v>
       </c>
-      <c r="H16" s="53" t="n">
+      <c r="H16" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I16" s="39" t="n">
@@ -10371,12 +10628,12 @@
         <v>0.539583333333333</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="K16" s="40" t="n">
         <v>0.125</v>
       </c>
-      <c r="L16" s="60" t="n">
+      <c r="L16" s="63" t="n">
         <f aca="false">IF(F16="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10416,21 +10673,21 @@
         <v>2.12676666666667</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="E17" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -10439,10 +10696,10 @@
       <c r="F17" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="66" t="n">
+      <c r="G17" s="69" t="n">
         <v>7.99</v>
       </c>
-      <c r="H17" s="53" t="n">
+      <c r="H17" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I17" s="39" t="n">
@@ -10450,12 +10707,12 @@
         <v>0.665833333333333</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="K17" s="40" t="n">
         <v>0.2</v>
       </c>
-      <c r="L17" s="60" t="n">
+      <c r="L17" s="63" t="n">
         <f aca="false">IF(F17="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10495,21 +10752,21 @@
         <v>1.84018666666667</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E18" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -10518,10 +10775,10 @@
       <c r="F18" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="66" t="n">
+      <c r="G18" s="69" t="n">
         <v>6.35</v>
       </c>
-      <c r="H18" s="53" t="n">
+      <c r="H18" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I18" s="39" t="n">
@@ -10529,12 +10786,12 @@
         <v>0.529166666666667</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="K18" s="40" t="n">
         <v>0.22</v>
       </c>
-      <c r="L18" s="60" t="n">
+      <c r="L18" s="63" t="n">
         <f aca="false">IF(F18="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10574,17 +10831,17 @@
         <v>2.00632</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B19" s="29"/>
       <c r="C19" s="29"/>
       <c r="D19" s="29"/>
-      <c r="E19" s="67" t="n">
+      <c r="E19" s="70" t="n">
         <f aca="false">SUM(E16:E18)</f>
         <v>3000</v>
       </c>
@@ -10623,19 +10880,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O20" s="27" t="n">
         <f aca="false">Inputs!$B$18*Inputs!$B$10+Inputs!$B$19</f>
         <v>1100.6</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -10660,43 +10917,43 @@
       <c r="V22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="65" t="s">
-        <v>432</v>
-      </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
+      <c r="A23" s="68" t="s">
+        <v>452</v>
+      </c>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="68"/>
+      <c r="Q23" s="68"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="68"/>
+      <c r="U23" s="68"/>
+      <c r="V23" s="68"/>
     </row>
     <row r="24" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>69</v>
@@ -10705,66 +10962,66 @@
         <v>20</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P24" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="E25" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -10773,20 +11030,20 @@
       <c r="F25" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G25" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H25" s="53"/>
+      <c r="G25" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H25" s="56"/>
       <c r="I25" s="40" t="n">
         <v>0.42</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="K25" s="40" t="n">
         <v>0.07</v>
       </c>
-      <c r="L25" s="60" t="n">
+      <c r="L25" s="63" t="n">
         <f aca="false">IF(F25="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10825,21 +11082,21 @@
         <v>2.12557333333333</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>440</v>
+        <v>460</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="E26" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -10848,20 +11105,20 @@
       <c r="F26" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G26" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H26" s="53"/>
+      <c r="G26" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H26" s="56"/>
       <c r="I26" s="40" t="n">
         <v>0.48</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="K26" s="40" t="n">
         <v>0.07</v>
       </c>
-      <c r="L26" s="60" t="n">
+      <c r="L26" s="63" t="n">
         <f aca="false">IF(F26="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10900,21 +11157,21 @@
         <v>2.04013333333333</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B27" s="37" t="s">
         <v>193</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>444</v>
+        <v>464</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E27" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -10923,20 +11180,20 @@
       <c r="F27" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H27" s="53"/>
+      <c r="G27" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H27" s="56"/>
       <c r="I27" s="40" t="n">
         <v>0.42</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="K27" s="40" t="n">
         <v>0.07</v>
       </c>
-      <c r="L27" s="60" t="n">
+      <c r="L27" s="63" t="n">
         <f aca="false">IF(F27="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -10975,17 +11232,17 @@
         <v>2.12557333333333</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B28" s="29"/>
       <c r="C28" s="29"/>
       <c r="D28" s="29"/>
-      <c r="E28" s="67" t="n">
+      <c r="E28" s="70" t="n">
         <f aca="false">SUM(E25:E27)</f>
         <v>3000</v>
       </c>
@@ -11024,19 +11281,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O29" s="27" t="n">
         <f aca="false">Inputs!$B$21+Inputs!$B$30</f>
         <v>1850</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -11061,43 +11318,43 @@
       <c r="V31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="65" t="s">
-        <v>448</v>
-      </c>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="65"/>
-      <c r="O32" s="65"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="65"/>
+      <c r="A32" s="68" t="s">
+        <v>468</v>
+      </c>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="68"/>
+      <c r="M32" s="68"/>
+      <c r="N32" s="68"/>
+      <c r="O32" s="68"/>
+      <c r="P32" s="68"/>
+      <c r="Q32" s="68"/>
+      <c r="R32" s="68"/>
+      <c r="S32" s="68"/>
+      <c r="T32" s="68"/>
+      <c r="U32" s="68"/>
+      <c r="V32" s="68"/>
     </row>
     <row r="33" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>69</v>
@@ -11106,66 +11363,66 @@
         <v>20</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P33" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E34" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -11174,22 +11431,22 @@
       <c r="F34" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H34" s="53" t="n">
+      <c r="G34" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H34" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I34" s="40" t="n">
         <v>0.96</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>450</v>
+        <v>470</v>
       </c>
       <c r="K34" s="40" t="n">
         <v>0.5</v>
       </c>
-      <c r="L34" s="60" t="n">
+      <c r="L34" s="63" t="n">
         <f aca="false">IF(F34="USD",Inputs!$B$10,1)</f>
         <v>1</v>
       </c>
@@ -11228,21 +11485,21 @@
         <v>1.88</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>451</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E35" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -11251,22 +11508,22 @@
       <c r="F35" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G35" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H35" s="53" t="n">
+      <c r="G35" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H35" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I35" s="40" t="n">
         <v>0.99</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>454</v>
+        <v>474</v>
       </c>
       <c r="K35" s="40" t="n">
         <v>0.25</v>
       </c>
-      <c r="L35" s="60" t="n">
+      <c r="L35" s="63" t="n">
         <f aca="false">IF(F35="USD",Inputs!$B$10,1)</f>
         <v>1</v>
       </c>
@@ -11305,21 +11562,21 @@
         <v>2.1</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>453</v>
+        <v>473</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E36" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -11328,22 +11585,22 @@
       <c r="F36" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G36" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H36" s="53" t="n">
+      <c r="G36" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H36" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I36" s="40" t="n">
         <v>0.99</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>456</v>
+        <v>476</v>
       </c>
       <c r="K36" s="40" t="n">
         <v>0.25</v>
       </c>
-      <c r="L36" s="60" t="n">
+      <c r="L36" s="63" t="n">
         <f aca="false">IF(F36="USD",Inputs!$B$10,1)</f>
         <v>1</v>
       </c>
@@ -11382,17 +11639,17 @@
         <v>2.1</v>
       </c>
       <c r="V36" s="11" t="s">
-        <v>457</v>
+        <v>477</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
       <c r="D37" s="29"/>
-      <c r="E37" s="67" t="n">
+      <c r="E37" s="70" t="n">
         <f aca="false">SUM(E34:E36)</f>
         <v>3000</v>
       </c>
@@ -11431,19 +11688,19 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O38" s="27" t="n">
         <f aca="false">Inputs!$B$20</f>
         <v>300</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -11468,43 +11725,43 @@
       <c r="V40" s="4"/>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="65" t="s">
-        <v>460</v>
-      </c>
-      <c r="B41" s="65"/>
-      <c r="C41" s="65"/>
-      <c r="D41" s="65"/>
-      <c r="E41" s="65"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="65"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="65"/>
-      <c r="K41" s="65"/>
-      <c r="L41" s="65"/>
-      <c r="M41" s="65"/>
-      <c r="N41" s="65"/>
-      <c r="O41" s="65"/>
-      <c r="P41" s="65"/>
-      <c r="Q41" s="65"/>
-      <c r="R41" s="65"/>
-      <c r="S41" s="65"/>
-      <c r="T41" s="65"/>
-      <c r="U41" s="65"/>
-      <c r="V41" s="65"/>
+      <c r="A41" s="68" t="s">
+        <v>480</v>
+      </c>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+      <c r="F41" s="68"/>
+      <c r="G41" s="68"/>
+      <c r="H41" s="68"/>
+      <c r="I41" s="68"/>
+      <c r="J41" s="68"/>
+      <c r="K41" s="68"/>
+      <c r="L41" s="68"/>
+      <c r="M41" s="68"/>
+      <c r="N41" s="68"/>
+      <c r="O41" s="68"/>
+      <c r="P41" s="68"/>
+      <c r="Q41" s="68"/>
+      <c r="R41" s="68"/>
+      <c r="S41" s="68"/>
+      <c r="T41" s="68"/>
+      <c r="U41" s="68"/>
+      <c r="V41" s="68"/>
     </row>
     <row r="42" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>69</v>
@@ -11513,66 +11770,66 @@
         <v>20</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K42" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O42" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P42" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S42" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T42" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U42" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V42" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B43" s="37" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E43" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -11581,22 +11838,22 @@
       <c r="F43" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G43" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H43" s="53" t="n">
+      <c r="G43" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H43" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I43" s="40" t="n">
         <v>1.67</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="K43" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="L43" s="60" t="n">
+      <c r="L43" s="63" t="n">
         <f aca="false">IF(F43="USD",Inputs!$B$10,1)</f>
         <v>1</v>
       </c>
@@ -11635,21 +11892,21 @@
         <v>1.67</v>
       </c>
       <c r="V43" s="11" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="21" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="B44" s="37" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E44" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -11658,22 +11915,22 @@
       <c r="F44" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G44" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H44" s="53" t="n">
+      <c r="G44" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H44" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I44" s="40" t="n">
         <v>2.35</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="K44" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="L44" s="60" t="n">
+      <c r="L44" s="63" t="n">
         <f aca="false">IF(F44="USD",Inputs!$B$10,1)</f>
         <v>1</v>
       </c>
@@ -11712,21 +11969,21 @@
         <v>0.99</v>
       </c>
       <c r="V44" s="11" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B45" s="37" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="D45" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E45" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -11735,22 +11992,22 @@
       <c r="F45" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="G45" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H45" s="53" t="n">
+      <c r="G45" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H45" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I45" s="40" t="n">
         <v>2.35</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="K45" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="60" t="n">
+      <c r="L45" s="63" t="n">
         <f aca="false">IF(F45="USD",Inputs!$B$10,1)</f>
         <v>1</v>
       </c>
@@ -11789,17 +12046,17 @@
         <v>0.99</v>
       </c>
       <c r="V45" s="11" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B46" s="29"/>
       <c r="C46" s="29"/>
       <c r="D46" s="29"/>
-      <c r="E46" s="67" t="n">
+      <c r="E46" s="70" t="n">
         <f aca="false">SUM(E43:E45)</f>
         <v>3000</v>
       </c>
@@ -11838,14 +12095,14 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O47" s="27" t="n">
         <f aca="false">Inputs!$B$20</f>
         <v>300</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -11902,17 +12159,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -11937,43 +12194,43 @@
       <c r="V4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="65" t="s">
-        <v>471</v>
-      </c>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
+      <c r="A5" s="68" t="s">
+        <v>491</v>
+      </c>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
     </row>
     <row r="6" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>69</v>
@@ -11982,66 +12239,66 @@
         <v>20</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P6" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q6" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R6" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S6" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T6" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V6" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>435</v>
+        <v>455</v>
       </c>
       <c r="E7" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -12050,20 +12307,20 @@
       <c r="F7" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H7" s="53"/>
+      <c r="G7" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H7" s="56"/>
       <c r="I7" s="40" t="n">
         <v>0.46</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>437</v>
+        <v>457</v>
       </c>
       <c r="K7" s="40" t="n">
         <v>0.07</v>
       </c>
-      <c r="L7" s="60" t="n">
+      <c r="L7" s="63" t="n">
         <f aca="false">IF(F7="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12102,21 +12359,21 @@
         <v>2.06861333333333</v>
       </c>
       <c r="V7" s="11" t="s">
-        <v>438</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>439</v>
+        <v>459</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="E8" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -12125,20 +12382,20 @@
       <c r="F8" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G8" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H8" s="53"/>
+      <c r="G8" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H8" s="56"/>
       <c r="I8" s="40" t="n">
         <v>0.6</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="K8" s="40" t="n">
         <v>0.07</v>
       </c>
-      <c r="L8" s="60" t="n">
+      <c r="L8" s="63" t="n">
         <f aca="false">IF(F8="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12177,21 +12434,21 @@
         <v>1.86925333333333</v>
       </c>
       <c r="V8" s="11" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B9" s="37" t="s">
         <v>193</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E9" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -12200,20 +12457,20 @@
       <c r="F9" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H9" s="53"/>
+      <c r="G9" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H9" s="56"/>
       <c r="I9" s="40" t="n">
         <v>0.55</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
       <c r="K9" s="40" t="n">
         <v>0.07</v>
       </c>
-      <c r="L9" s="60" t="n">
+      <c r="L9" s="63" t="n">
         <f aca="false">IF(F9="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12252,17 +12509,17 @@
         <v>1.94045333333333</v>
       </c>
       <c r="V9" s="11" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B10" s="29"/>
       <c r="C10" s="29"/>
       <c r="D10" s="29"/>
-      <c r="E10" s="67" t="n">
+      <c r="E10" s="70" t="n">
         <f aca="false">SUM(E7:E9)</f>
         <v>3000</v>
       </c>
@@ -12301,19 +12558,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O11" s="27" t="n">
         <f aca="false">Inputs!$B$21+Inputs!$B$30</f>
         <v>1850</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>446</v>
+        <v>466</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -12338,43 +12595,43 @@
       <c r="V13" s="4"/>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="65" t="s">
-        <v>476</v>
-      </c>
-      <c r="B14" s="65"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
-      <c r="L14" s="65"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="65"/>
-      <c r="P14" s="65"/>
-      <c r="Q14" s="65"/>
-      <c r="R14" s="65"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="65"/>
-      <c r="U14" s="65"/>
-      <c r="V14" s="65"/>
+      <c r="A14" s="68" t="s">
+        <v>496</v>
+      </c>
+      <c r="B14" s="68"/>
+      <c r="C14" s="68"/>
+      <c r="D14" s="68"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="68"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="68"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="68"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="68"/>
+      <c r="P14" s="68"/>
+      <c r="Q14" s="68"/>
+      <c r="R14" s="68"/>
+      <c r="S14" s="68"/>
+      <c r="T14" s="68"/>
+      <c r="U14" s="68"/>
+      <c r="V14" s="68"/>
     </row>
     <row r="15" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>69</v>
@@ -12383,66 +12640,66 @@
         <v>20</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P15" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S15" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T15" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U15" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V15" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B16" s="37" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E16" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -12451,10 +12708,10 @@
       <c r="F16" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G16" s="66" t="n">
+      <c r="G16" s="69" t="n">
         <v>11.45</v>
       </c>
-      <c r="H16" s="53" t="n">
+      <c r="H16" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I16" s="39" t="n">
@@ -12462,12 +12719,12 @@
         <v>0.477083333333333</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="K16" s="40" t="n">
         <v>0.14</v>
       </c>
-      <c r="L16" s="60" t="n">
+      <c r="L16" s="63" t="n">
         <f aca="false">IF(F16="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12475,7 +12732,7 @@
         <f aca="false">(I16+K16)*L16*(1+Inputs!$B$33)</f>
         <v>0.878726666666667</v>
       </c>
-      <c r="N16" s="69" t="n">
+      <c r="N16" s="42" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>0.45</v>
       </c>
@@ -12508,21 +12765,21 @@
         <v>0.994406666666667</v>
       </c>
       <c r="V16" s="11" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B17" s="37" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="E17" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -12531,10 +12788,10 @@
       <c r="F17" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="66" t="n">
+      <c r="G17" s="69" t="n">
         <v>8.13</v>
       </c>
-      <c r="H17" s="53" t="n">
+      <c r="H17" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I17" s="39" t="n">
@@ -12542,12 +12799,12 @@
         <v>0.6775</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="K17" s="40" t="n">
         <v>0.13</v>
       </c>
-      <c r="L17" s="60" t="n">
+      <c r="L17" s="63" t="n">
         <f aca="false">IF(F17="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12555,7 +12812,7 @@
         <f aca="false">(I17+K17)*L17*(1+Inputs!$B$33)</f>
         <v>1.14988</v>
       </c>
-      <c r="N17" s="69" t="n">
+      <c r="N17" s="42" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>0.45</v>
       </c>
@@ -12588,21 +12845,21 @@
         <v>0.723253333333334</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E18" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -12611,10 +12868,10 @@
       <c r="F18" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="66" t="n">
+      <c r="G18" s="69" t="n">
         <v>5.29</v>
       </c>
-      <c r="H18" s="53" t="n">
+      <c r="H18" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I18" s="39" t="n">
@@ -12622,12 +12879,12 @@
         <v>0.440833333333333</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="K18" s="40" t="n">
         <v>0.17</v>
       </c>
-      <c r="L18" s="60" t="n">
+      <c r="L18" s="63" t="n">
         <f aca="false">IF(F18="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12635,7 +12892,7 @@
         <f aca="false">(I18+K18)*L18*(1+Inputs!$B$33)</f>
         <v>0.869826666666667</v>
       </c>
-      <c r="N18" s="69" t="n">
+      <c r="N18" s="42" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>0.45</v>
       </c>
@@ -12668,17 +12925,17 @@
         <v>1.00330666666667</v>
       </c>
       <c r="V18" s="11" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B19" s="29"/>
       <c r="C19" s="29"/>
       <c r="D19" s="29"/>
-      <c r="E19" s="67" t="n">
+      <c r="E19" s="70" t="n">
         <f aca="false">SUM(E16:E18)</f>
         <v>3000</v>
       </c>
@@ -12717,19 +12974,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O20" s="27" t="n">
         <f aca="false">Inputs!$B$18*Inputs!$B$10+Inputs!$B$19+Inputs!$B$38*Inputs!$B$9+Inputs!$B$39</f>
         <v>3350.6</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -12754,43 +13011,43 @@
       <c r="V22" s="4"/>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="65" t="s">
-        <v>480</v>
-      </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="65"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="65"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="65"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="65"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="65"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="65"/>
-      <c r="S23" s="65"/>
-      <c r="T23" s="65"/>
-      <c r="U23" s="65"/>
-      <c r="V23" s="65"/>
+      <c r="A23" s="68" t="s">
+        <v>500</v>
+      </c>
+      <c r="B23" s="68"/>
+      <c r="C23" s="68"/>
+      <c r="D23" s="68"/>
+      <c r="E23" s="68"/>
+      <c r="F23" s="68"/>
+      <c r="G23" s="68"/>
+      <c r="H23" s="68"/>
+      <c r="I23" s="68"/>
+      <c r="J23" s="68"/>
+      <c r="K23" s="68"/>
+      <c r="L23" s="68"/>
+      <c r="M23" s="68"/>
+      <c r="N23" s="68"/>
+      <c r="O23" s="68"/>
+      <c r="P23" s="68"/>
+      <c r="Q23" s="68"/>
+      <c r="R23" s="68"/>
+      <c r="S23" s="68"/>
+      <c r="T23" s="68"/>
+      <c r="U23" s="68"/>
+      <c r="V23" s="68"/>
     </row>
     <row r="24" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>69</v>
@@ -12799,66 +13056,66 @@
         <v>20</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O24" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P24" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S24" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T24" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U24" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V24" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B25" s="37" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E25" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -12867,10 +13124,10 @@
       <c r="F25" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G25" s="66" t="n">
+      <c r="G25" s="69" t="n">
         <v>12.95</v>
       </c>
-      <c r="H25" s="53" t="n">
+      <c r="H25" s="56" t="n">
         <v>24</v>
       </c>
       <c r="I25" s="39" t="n">
@@ -12878,12 +13135,12 @@
         <v>0.539583333333333</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="K25" s="40" t="n">
         <v>0.125</v>
       </c>
-      <c r="L25" s="60" t="n">
+      <c r="L25" s="63" t="n">
         <f aca="false">IF(F25="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12891,7 +13148,7 @@
         <f aca="false">(I25+K25)*L25*(1+Inputs!$B$33)</f>
         <v>0.946366666666667</v>
       </c>
-      <c r="N25" s="69" t="n">
+      <c r="N25" s="42" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>0.45</v>
       </c>
@@ -12924,21 +13181,21 @@
         <v>0.926766666666667</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>365</v>
+        <v>385</v>
       </c>
       <c r="E26" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -12947,10 +13204,10 @@
       <c r="F26" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G26" s="66" t="n">
+      <c r="G26" s="69" t="n">
         <v>7.99</v>
       </c>
-      <c r="H26" s="53" t="n">
+      <c r="H26" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I26" s="39" t="n">
@@ -12958,12 +13215,12 @@
         <v>0.665833333333333</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>428</v>
+        <v>448</v>
       </c>
       <c r="K26" s="40" t="n">
         <v>0.2</v>
       </c>
-      <c r="L26" s="60" t="n">
+      <c r="L26" s="63" t="n">
         <f aca="false">IF(F26="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -12971,7 +13228,7 @@
         <f aca="false">(I26+K26)*L26*(1+Inputs!$B$33)</f>
         <v>1.23294666666667</v>
       </c>
-      <c r="N26" s="69" t="n">
+      <c r="N26" s="42" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>0.45</v>
       </c>
@@ -13004,21 +13261,21 @@
         <v>0.640186666666667</v>
       </c>
       <c r="V26" s="11" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B27" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E27" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -13027,10 +13284,10 @@
       <c r="F27" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G27" s="66" t="n">
+      <c r="G27" s="69" t="n">
         <v>6.35</v>
       </c>
-      <c r="H27" s="53" t="n">
+      <c r="H27" s="56" t="n">
         <v>12</v>
       </c>
       <c r="I27" s="39" t="n">
@@ -13038,12 +13295,12 @@
         <v>0.529166666666667</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="K27" s="40" t="n">
         <v>0.22</v>
       </c>
-      <c r="L27" s="60" t="n">
+      <c r="L27" s="63" t="n">
         <f aca="false">IF(F27="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -13051,7 +13308,7 @@
         <f aca="false">(I27+K27)*L27*(1+Inputs!$B$33)</f>
         <v>1.06681333333333</v>
       </c>
-      <c r="N27" s="69" t="n">
+      <c r="N27" s="42" t="n">
         <f aca="false">Inputs!$B$37</f>
         <v>0.45</v>
       </c>
@@ -13084,17 +13341,17 @@
         <v>0.80632</v>
       </c>
       <c r="V27" s="11" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B28" s="29"/>
       <c r="C28" s="29"/>
       <c r="D28" s="29"/>
-      <c r="E28" s="67" t="n">
+      <c r="E28" s="70" t="n">
         <f aca="false">SUM(E25:E27)</f>
         <v>3000</v>
       </c>
@@ -13133,19 +13390,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O29" s="27" t="n">
         <f aca="false">Inputs!$B$18*Inputs!$B$10+Inputs!$B$19+Inputs!$B$38*Inputs!$B$9+Inputs!$B$39</f>
         <v>3350.6</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -13170,43 +13427,43 @@
       <c r="V31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="65" t="s">
-        <v>482</v>
-      </c>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="65"/>
-      <c r="O32" s="65"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="65"/>
+      <c r="A32" s="68" t="s">
+        <v>502</v>
+      </c>
+      <c r="B32" s="68"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68"/>
+      <c r="L32" s="68"/>
+      <c r="M32" s="68"/>
+      <c r="N32" s="68"/>
+      <c r="O32" s="68"/>
+      <c r="P32" s="68"/>
+      <c r="Q32" s="68"/>
+      <c r="R32" s="68"/>
+      <c r="S32" s="68"/>
+      <c r="T32" s="68"/>
+      <c r="U32" s="68"/>
+      <c r="V32" s="68"/>
     </row>
     <row r="33" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>69</v>
@@ -13215,66 +13472,66 @@
         <v>20</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="P33" s="7" t="s">
         <v>157</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="S33" s="7" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="T33" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="U33" s="7" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="V33" s="7" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="E34" s="26" t="n">
         <f aca="false">Inputs!$B$5</f>
@@ -13283,22 +13540,22 @@
       <c r="F34" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G34" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H34" s="53" t="n">
+      <c r="G34" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H34" s="56" t="n">
         <v>90</v>
       </c>
       <c r="I34" s="40" t="n">
         <v>0.75</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="K34" s="40" t="n">
         <v>0.15</v>
       </c>
-      <c r="L34" s="60" t="n">
+      <c r="L34" s="63" t="n">
         <f aca="false">IF(F34="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -13338,21 +13595,21 @@
         <v>1.79153333333333</v>
       </c>
       <c r="V34" s="11" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>452</v>
+        <v>472</v>
       </c>
       <c r="B35" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E35" s="26" t="n">
         <f aca="false">Inputs!$B$6</f>
@@ -13361,22 +13618,22 @@
       <c r="F35" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G35" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H35" s="53" t="n">
+      <c r="G35" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H35" s="56" t="n">
         <v>72</v>
       </c>
       <c r="I35" s="40" t="n">
         <v>1.57</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="K35" s="40" t="n">
         <v>0.15</v>
       </c>
-      <c r="L35" s="60" t="n">
+      <c r="L35" s="63" t="n">
         <f aca="false">IF(F35="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -13416,21 +13673,21 @@
         <v>0.623853333333334</v>
       </c>
       <c r="V35" s="11" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="D36" s="21" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="E36" s="26" t="n">
         <f aca="false">Inputs!$B$7</f>
@@ -13439,22 +13696,22 @@
       <c r="F36" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="G36" s="68" t="s">
-        <v>436</v>
-      </c>
-      <c r="H36" s="53" t="n">
+      <c r="G36" s="41" t="s">
+        <v>456</v>
+      </c>
+      <c r="H36" s="56" t="n">
         <v>72</v>
       </c>
       <c r="I36" s="40" t="n">
         <v>1.57</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="K36" s="40" t="n">
         <v>0.31</v>
       </c>
-      <c r="L36" s="60" t="n">
+      <c r="L36" s="63" t="n">
         <f aca="false">IF(F36="USD",Inputs!$B$10,1)</f>
         <v>1.424</v>
       </c>
@@ -13494,17 +13751,17 @@
         <v>0.396013333333334</v>
       </c>
       <c r="V36" s="11" t="s">
-        <v>489</v>
+        <v>509</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="28" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="B37" s="29"/>
       <c r="C37" s="29"/>
       <c r="D37" s="29"/>
-      <c r="E37" s="67" t="n">
+      <c r="E37" s="70" t="n">
         <f aca="false">SUM(E34:E36)</f>
         <v>3000</v>
       </c>
@@ -13543,14 +13800,14 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="O38" s="27" t="n">
         <f aca="false">Inputs!$B$18*Inputs!$B$10+Inputs!$B$19</f>
         <v>1100.6</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -13601,51 +13858,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>490</v>
+        <v>510</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>491</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>492</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="60" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="57" t="s">
-        <v>260</v>
-      </c>
-      <c r="C5" s="57" t="s">
-        <v>493</v>
-      </c>
-      <c r="D5" s="57" t="s">
-        <v>494</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>495</v>
-      </c>
-      <c r="F5" s="57" t="s">
-        <v>496</v>
-      </c>
-      <c r="G5" s="57" t="s">
-        <v>497</v>
-      </c>
-      <c r="H5" s="57" t="s">
-        <v>498</v>
+      <c r="B5" s="60" t="s">
+        <v>280</v>
+      </c>
+      <c r="C5" s="60" t="s">
+        <v>513</v>
+      </c>
+      <c r="D5" s="60" t="s">
+        <v>514</v>
+      </c>
+      <c r="E5" s="60" t="s">
+        <v>515</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>516</v>
+      </c>
+      <c r="G5" s="60" t="s">
+        <v>517</v>
+      </c>
+      <c r="H5" s="60" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="C6" s="27" t="n">
         <f aca="false">N31</f>
@@ -13668,15 +13925,15 @@
         <v>1.28930222222222</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="47" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7" s="47" t="s">
-        <v>501</v>
+      <c r="A7" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>521</v>
       </c>
       <c r="C7" s="33" t="n">
         <f aca="false">N38</f>
@@ -13698,16 +13955,16 @@
         <f aca="false">J38</f>
         <v>1.56464666666667</v>
       </c>
-      <c r="H7" s="70" t="s">
-        <v>500</v>
+      <c r="H7" s="71" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="47" t="s">
-        <v>502</v>
+      <c r="A8" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>522</v>
       </c>
       <c r="C8" s="33" t="n">
         <f aca="false">N45</f>
@@ -13729,16 +13986,16 @@
         <f aca="false">J45</f>
         <v>1.57222</v>
       </c>
-      <c r="H8" s="70" t="s">
-        <v>500</v>
+      <c r="H8" s="71" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="C9" s="27" t="n">
         <f aca="false">N52</f>
@@ -13761,15 +14018,15 @@
         <v>1.52554444444444</v>
       </c>
       <c r="H9" s="21" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="C10" s="27" t="n">
         <f aca="false">N59</f>
@@ -13792,15 +14049,15 @@
         <v>1.40570666666667</v>
       </c>
       <c r="H10" s="21" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="C11" s="27" t="n">
         <f aca="false">N66</f>
@@ -13823,15 +14080,15 @@
         <v>1.32866666666667</v>
       </c>
       <c r="H11" s="21" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="C12" s="27" t="n">
         <f aca="false">N74</f>
@@ -13854,15 +14111,15 @@
         <v>2.48930222222222</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="47" t="s">
-        <v>270</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>509</v>
+      <c r="A13" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>529</v>
       </c>
       <c r="C13" s="33" t="n">
         <f aca="false">N81</f>
@@ -13884,16 +14141,16 @@
         <f aca="false">J81</f>
         <v>2.02514</v>
       </c>
-      <c r="H13" s="70" t="s">
-        <v>500</v>
+      <c r="H13" s="71" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="B14" s="47" t="s">
-        <v>510</v>
+      <c r="A14" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="B14" s="50" t="s">
+        <v>530</v>
       </c>
       <c r="C14" s="33" t="n">
         <f aca="false">N88</f>
@@ -13915,16 +14172,16 @@
         <f aca="false">J88</f>
         <v>2.03034</v>
       </c>
-      <c r="H14" s="70" t="s">
-        <v>500</v>
+      <c r="H14" s="71" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="C15" s="27" t="n">
         <f aca="false">N95</f>
@@ -13947,15 +14204,15 @@
         <v>1.98366444444444</v>
       </c>
       <c r="H15" s="21" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="C16" s="27" t="n">
         <f aca="false">N102</f>
@@ -13978,15 +14235,15 @@
         <v>1.89321333333333</v>
       </c>
       <c r="H16" s="21" t="s">
-        <v>513</v>
+        <v>533</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="37" t="s">
-        <v>514</v>
+        <v>534</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>515</v>
+        <v>535</v>
       </c>
       <c r="C17" s="27" t="n">
         <f aca="false">N109</f>
@@ -14009,47 +14266,47 @@
         <v>1.42597333333333</v>
       </c>
       <c r="H17" s="21" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>516</v>
+        <v>536</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="36" t="s">
-        <v>517</v>
+        <v>537</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="36" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="36" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="36" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="36" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
-        <v>522</v>
+      <c r="A25" s="72" t="s">
+        <v>542</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -14068,7 +14325,7 @@
     </row>
     <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>61</v>
@@ -14080,7 +14337,7 @@
         <v>19</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>24</v>
@@ -14098,19 +14355,19 @@
         <v>157</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14118,7 +14375,7 @@
         <v>73</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="C28" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B7</f>
@@ -14131,7 +14388,7 @@
         <f aca="false">'Regular Finish – Top 3'!I7+'Regular Finish – Top 3'!K7</f>
         <v>0.617083333333333</v>
       </c>
-      <c r="F28" s="72" t="n">
+      <c r="F28" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L7</f>
         <v>1.424</v>
       </c>
@@ -14176,7 +14433,7 @@
         <v>75</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="C29" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
@@ -14189,7 +14446,7 @@
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
         <v>0.8075</v>
       </c>
-      <c r="F29" s="72" t="n">
+      <c r="F29" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -14234,7 +14491,7 @@
         <v>166</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="C30" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B9</f>
@@ -14247,7 +14504,7 @@
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
         <v>0.610833333333333</v>
       </c>
-      <c r="F30" s="72" t="n">
+      <c r="F30" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L9</f>
         <v>1.424</v>
       </c>
@@ -14289,7 +14546,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B31" s="29"/>
       <c r="C31" s="29"/>
@@ -14308,7 +14565,7 @@
         <f aca="false">O31/M31</f>
         <v>1.64846666666667</v>
       </c>
-      <c r="M31" s="67" t="n">
+      <c r="M31" s="70" t="n">
         <f aca="false">SUM(M28:M30)</f>
         <v>3000</v>
       </c>
@@ -14323,7 +14580,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -14342,7 +14599,7 @@
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>61</v>
@@ -14354,7 +14611,7 @@
         <v>19</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>24</v>
@@ -14372,19 +14629,19 @@
         <v>157</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N34" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O34" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14399,13 +14656,13 @@
         <v>120 ml</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E35" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
         <v>0.49</v>
       </c>
-      <c r="F35" s="72" t="n">
+      <c r="F35" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L25</f>
         <v>1.424</v>
       </c>
@@ -14449,7 +14706,7 @@
         <v>75</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="C36" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
@@ -14462,7 +14719,7 @@
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
         <v>0.8075</v>
       </c>
-      <c r="F36" s="72" t="n">
+      <c r="F36" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -14514,13 +14771,13 @@
         <v>250 ml</v>
       </c>
       <c r="D37" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E37" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I27+'Regular Finish – Top 3'!K27</f>
         <v>0.49</v>
       </c>
-      <c r="F37" s="72" t="n">
+      <c r="F37" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L27</f>
         <v>1.424</v>
       </c>
@@ -14561,7 +14818,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B38" s="29"/>
       <c r="C38" s="29"/>
@@ -14580,7 +14837,7 @@
         <f aca="false">O38/M38</f>
         <v>1.64504333333333</v>
       </c>
-      <c r="M38" s="67" t="n">
+      <c r="M38" s="70" t="n">
         <f aca="false">SUM(M35:M37)</f>
         <v>3000</v>
       </c>
@@ -14595,7 +14852,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="s">
-        <v>532</v>
+        <v>552</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -14614,7 +14871,7 @@
     </row>
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>61</v>
@@ -14626,7 +14883,7 @@
         <v>19</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>24</v>
@@ -14644,19 +14901,19 @@
         <v>157</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O41" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14671,13 +14928,13 @@
         <v>120 ml</v>
       </c>
       <c r="D42" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E42" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
         <v>0.49</v>
       </c>
-      <c r="F42" s="72" t="n">
+      <c r="F42" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L25</f>
         <v>1.424</v>
       </c>
@@ -14728,13 +14985,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E43" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
         <v>0.55</v>
       </c>
-      <c r="F43" s="72" t="n">
+      <c r="F43" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L26</f>
         <v>1.424</v>
       </c>
@@ -14778,7 +15035,7 @@
         <v>166</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="C44" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
@@ -14791,7 +15048,7 @@
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
         <v>0.8075</v>
       </c>
-      <c r="F44" s="72" t="n">
+      <c r="F44" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -14833,7 +15090,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B45" s="29"/>
       <c r="C45" s="29"/>
@@ -14852,7 +15109,7 @@
         <f aca="false">O45/M45</f>
         <v>1.65261666666667</v>
       </c>
-      <c r="M45" s="67" t="n">
+      <c r="M45" s="70" t="n">
         <f aca="false">SUM(M42:M44)</f>
         <v>3000</v>
       </c>
@@ -14867,7 +15124,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -14886,7 +15143,7 @@
     </row>
     <row r="48" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>61</v>
@@ -14898,7 +15155,7 @@
         <v>19</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>24</v>
@@ -14916,19 +15173,19 @@
         <v>157</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M48" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O48" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14943,13 +15200,13 @@
         <v>120 ml</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E49" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
         <v>0.49</v>
       </c>
-      <c r="F49" s="72" t="n">
+      <c r="F49" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L25</f>
         <v>1.424</v>
       </c>
@@ -15000,13 +15257,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E50" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
         <v>0.55</v>
       </c>
-      <c r="F50" s="72" t="n">
+      <c r="F50" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L26</f>
         <v>1.424</v>
       </c>
@@ -15050,7 +15307,7 @@
         <v>166</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="C51" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B9</f>
@@ -15063,7 +15320,7 @@
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
         <v>0.610833333333333</v>
       </c>
-      <c r="F51" s="72" t="n">
+      <c r="F51" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L9</f>
         <v>1.424</v>
       </c>
@@ -15105,7 +15362,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -15124,7 +15381,7 @@
         <f aca="false">O52/M52</f>
         <v>1.57785666666667</v>
       </c>
-      <c r="M52" s="67" t="n">
+      <c r="M52" s="70" t="n">
         <f aca="false">SUM(M49:M51)</f>
         <v>3000</v>
       </c>
@@ -15139,7 +15396,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -15158,7 +15415,7 @@
     </row>
     <row r="55" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>61</v>
@@ -15170,7 +15427,7 @@
         <v>19</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>24</v>
@@ -15188,19 +15445,19 @@
         <v>157</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M55" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O55" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15215,13 +15472,13 @@
         <v>120 ml</v>
       </c>
       <c r="D56" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E56" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
         <v>0.49</v>
       </c>
-      <c r="F56" s="72" t="n">
+      <c r="F56" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L25</f>
         <v>1.424</v>
       </c>
@@ -15272,13 +15529,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E57" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
         <v>0.55</v>
       </c>
-      <c r="F57" s="72" t="n">
+      <c r="F57" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L26</f>
         <v>1.424</v>
       </c>
@@ -15322,7 +15579,7 @@
         <v>166</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="C58" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B36</f>
@@ -15335,7 +15592,7 @@
         <f aca="false">'Regular Finish – Top 3'!I36+'Regular Finish – Top 3'!K36</f>
         <v>1.24</v>
       </c>
-      <c r="F58" s="72" t="n">
+      <c r="F58" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L36</f>
         <v>1</v>
       </c>
@@ -15376,7 +15633,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B59" s="29"/>
       <c r="C59" s="29"/>
@@ -15395,7 +15652,7 @@
         <f aca="false">O59/M59</f>
         <v>1.40570666666667</v>
       </c>
-      <c r="M59" s="67" t="n">
+      <c r="M59" s="70" t="n">
         <f aca="false">SUM(M56:M58)</f>
         <v>3000</v>
       </c>
@@ -15410,7 +15667,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>537</v>
+        <v>557</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -15429,7 +15686,7 @@
     </row>
     <row r="62" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>61</v>
@@ -15441,7 +15698,7 @@
         <v>19</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>24</v>
@@ -15459,19 +15716,19 @@
         <v>157</v>
       </c>
       <c r="K62" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M62" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N62" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O62" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15486,13 +15743,13 @@
         <v>120 ml</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E63" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I25+'Regular Finish – Top 3'!K25</f>
         <v>0.49</v>
       </c>
-      <c r="F63" s="72" t="n">
+      <c r="F63" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L25</f>
         <v>1.424</v>
       </c>
@@ -15543,13 +15800,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E64" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I26+'Regular Finish – Top 3'!K26</f>
         <v>0.55</v>
       </c>
-      <c r="F64" s="72" t="n">
+      <c r="F64" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L26</f>
         <v>1.424</v>
       </c>
@@ -15600,13 +15857,13 @@
         <v>250 ml</v>
       </c>
       <c r="D65" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E65" s="23" t="n">
         <f aca="false">'Regular Finish – Top 3'!I27+'Regular Finish – Top 3'!K27</f>
         <v>0.49</v>
       </c>
-      <c r="F65" s="72" t="n">
+      <c r="F65" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L27</f>
         <v>1.424</v>
       </c>
@@ -15647,7 +15904,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B66" s="29"/>
       <c r="C66" s="29"/>
@@ -15666,7 +15923,7 @@
         <f aca="false">O66/M66</f>
         <v>1.32866666666667</v>
       </c>
-      <c r="M66" s="67" t="n">
+      <c r="M66" s="70" t="n">
         <f aca="false">SUM(M63:M65)</f>
         <v>3000</v>
       </c>
@@ -15680,13 +15937,13 @@
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="71" t="s">
-        <v>538</v>
+      <c r="A68" s="72" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -15705,7 +15962,7 @@
     </row>
     <row r="70" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>61</v>
@@ -15717,7 +15974,7 @@
         <v>19</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>24</v>
@@ -15735,19 +15992,19 @@
         <v>157</v>
       </c>
       <c r="K70" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M70" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O70" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15768,7 +16025,7 @@
         <f aca="false">'Regular Finish – Top 3'!I7+'Regular Finish – Top 3'!K7</f>
         <v>0.617083333333333</v>
       </c>
-      <c r="F71" s="72" t="n">
+      <c r="F71" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L7</f>
         <v>1.424</v>
       </c>
@@ -15827,7 +16084,7 @@
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
         <v>0.8075</v>
       </c>
-      <c r="F72" s="72" t="n">
+      <c r="F72" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -15886,7 +16143,7 @@
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
         <v>0.610833333333333</v>
       </c>
-      <c r="F73" s="72" t="n">
+      <c r="F73" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L9</f>
         <v>1.424</v>
       </c>
@@ -15929,7 +16186,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B74" s="29"/>
       <c r="C74" s="29"/>
@@ -15948,7 +16205,7 @@
         <f aca="false">O74/M74</f>
         <v>2.84846666666667</v>
       </c>
-      <c r="M74" s="67" t="n">
+      <c r="M74" s="70" t="n">
         <f aca="false">SUM(M71:M73)</f>
         <v>3000</v>
       </c>
@@ -15963,7 +16220,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="s">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -15982,7 +16239,7 @@
     </row>
     <row r="77" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>61</v>
@@ -15994,7 +16251,7 @@
         <v>19</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>24</v>
@@ -16012,19 +16269,19 @@
         <v>157</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M77" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N77" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O77" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16039,13 +16296,13 @@
         <v>120 ml</v>
       </c>
       <c r="D78" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E78" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
         <v>0.53</v>
       </c>
-      <c r="F78" s="72" t="n">
+      <c r="F78" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L7</f>
         <v>1.424</v>
       </c>
@@ -16089,7 +16346,7 @@
         <v>75</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="C79" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
@@ -16102,7 +16359,7 @@
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
         <v>0.8075</v>
       </c>
-      <c r="F79" s="72" t="n">
+      <c r="F79" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -16155,13 +16412,13 @@
         <v>250 ml</v>
       </c>
       <c r="D80" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E80" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I9+'Frosted Finish – Top 3'!K9</f>
         <v>0.62</v>
       </c>
-      <c r="F80" s="72" t="n">
+      <c r="F80" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L9</f>
         <v>1.424</v>
       </c>
@@ -16202,7 +16459,7 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B81" s="29"/>
       <c r="C81" s="29"/>
@@ -16221,7 +16478,7 @@
         <f aca="false">O81/M81</f>
         <v>2.10553666666667</v>
       </c>
-      <c r="M81" s="67" t="n">
+      <c r="M81" s="70" t="n">
         <f aca="false">SUM(M78:M80)</f>
         <v>3000</v>
       </c>
@@ -16236,7 +16493,7 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -16255,7 +16512,7 @@
     </row>
     <row r="84" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>61</v>
@@ -16267,7 +16524,7 @@
         <v>19</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>24</v>
@@ -16285,19 +16542,19 @@
         <v>157</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M84" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N84" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O84" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16312,13 +16569,13 @@
         <v>120 ml</v>
       </c>
       <c r="D85" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E85" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
         <v>0.53</v>
       </c>
-      <c r="F85" s="72" t="n">
+      <c r="F85" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L7</f>
         <v>1.424</v>
       </c>
@@ -16369,13 +16626,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D86" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E86" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
         <v>0.67</v>
       </c>
-      <c r="F86" s="72" t="n">
+      <c r="F86" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -16419,7 +16676,7 @@
         <v>166</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="C87" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B8</f>
@@ -16432,7 +16689,7 @@
         <f aca="false">'Regular Finish – Top 3'!I8+'Regular Finish – Top 3'!K8</f>
         <v>0.8075</v>
       </c>
-      <c r="F87" s="72" t="n">
+      <c r="F87" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -16475,7 +16732,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B88" s="29"/>
       <c r="C88" s="29"/>
@@ -16494,7 +16751,7 @@
         <f aca="false">O88/M88</f>
         <v>2.11073666666667</v>
       </c>
-      <c r="M88" s="67" t="n">
+      <c r="M88" s="70" t="n">
         <f aca="false">SUM(M85:M87)</f>
         <v>3000</v>
       </c>
@@ -16509,7 +16766,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -16528,7 +16785,7 @@
     </row>
     <row r="91" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>61</v>
@@ -16540,7 +16797,7 @@
         <v>19</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>24</v>
@@ -16558,19 +16815,19 @@
         <v>157</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M91" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N91" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O91" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16585,13 +16842,13 @@
         <v>120 ml</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E92" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
         <v>0.53</v>
       </c>
-      <c r="F92" s="72" t="n">
+      <c r="F92" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L7</f>
         <v>1.424</v>
       </c>
@@ -16642,13 +16899,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E93" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
         <v>0.67</v>
       </c>
-      <c r="F93" s="72" t="n">
+      <c r="F93" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -16692,7 +16949,7 @@
         <v>166</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="C94" s="22" t="str">
         <f aca="false">'Regular Finish – Top 3'!B9</f>
@@ -16705,7 +16962,7 @@
         <f aca="false">'Regular Finish – Top 3'!I9+'Regular Finish – Top 3'!K9</f>
         <v>0.610833333333333</v>
       </c>
-      <c r="F94" s="72" t="n">
+      <c r="F94" s="73" t="n">
         <f aca="false">'Regular Finish – Top 3'!L9</f>
         <v>1.424</v>
       </c>
@@ -16748,7 +17005,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B95" s="29"/>
       <c r="C95" s="29"/>
@@ -16767,7 +17024,7 @@
         <f aca="false">O95/M95</f>
         <v>2.03597666666667</v>
       </c>
-      <c r="M95" s="67" t="n">
+      <c r="M95" s="70" t="n">
         <f aca="false">SUM(M92:M94)</f>
         <v>3000</v>
       </c>
@@ -16782,7 +17039,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -16801,7 +17058,7 @@
     </row>
     <row r="98" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>61</v>
@@ -16813,7 +17070,7 @@
         <v>19</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>24</v>
@@ -16831,19 +17088,19 @@
         <v>157</v>
       </c>
       <c r="K98" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L98" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M98" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N98" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O98" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16858,13 +17115,13 @@
         <v>120 ml</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E99" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
         <v>0.53</v>
       </c>
-      <c r="F99" s="72" t="n">
+      <c r="F99" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L7</f>
         <v>1.424</v>
       </c>
@@ -16915,13 +17172,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E100" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
         <v>0.67</v>
       </c>
-      <c r="F100" s="72" t="n">
+      <c r="F100" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -16965,7 +17222,7 @@
         <v>166</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="C101" s="22" t="str">
         <f aca="false">'Frosted Finish – Top 3'!B36</f>
@@ -16978,7 +17235,7 @@
         <f aca="false">'Frosted Finish – Top 3'!I36+'Frosted Finish – Top 3'!K36</f>
         <v>1.88</v>
       </c>
-      <c r="F101" s="72" t="n">
+      <c r="F101" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L36</f>
         <v>1.424</v>
       </c>
@@ -17020,7 +17277,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B102" s="29"/>
       <c r="C102" s="29"/>
@@ -17039,7 +17296,7 @@
         <f aca="false">O102/M102</f>
         <v>2.07952</v>
       </c>
-      <c r="M102" s="67" t="n">
+      <c r="M102" s="70" t="n">
         <f aca="false">SUM(M99:M101)</f>
         <v>3000</v>
       </c>
@@ -17054,7 +17311,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -17073,7 +17330,7 @@
     </row>
     <row r="105" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="7" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>61</v>
@@ -17085,7 +17342,7 @@
         <v>19</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>24</v>
@@ -17103,19 +17360,19 @@
         <v>157</v>
       </c>
       <c r="K105" s="7" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="L105" s="7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="M105" s="7" t="s">
         <v>69</v>
       </c>
       <c r="N105" s="7" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="O105" s="7" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17130,13 +17387,13 @@
         <v>120 ml</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E106" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I7+'Frosted Finish – Top 3'!K7</f>
         <v>0.53</v>
       </c>
-      <c r="F106" s="72" t="n">
+      <c r="F106" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L7</f>
         <v>1.424</v>
       </c>
@@ -17187,13 +17444,13 @@
         <v>180–190 ml</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E107" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I8+'Frosted Finish – Top 3'!K8</f>
         <v>0.67</v>
       </c>
-      <c r="F107" s="72" t="n">
+      <c r="F107" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L8</f>
         <v>1.424</v>
       </c>
@@ -17244,13 +17501,13 @@
         <v>250 ml</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E108" s="23" t="n">
         <f aca="false">'Frosted Finish – Top 3'!I9+'Frosted Finish – Top 3'!K9</f>
         <v>0.62</v>
       </c>
-      <c r="F108" s="72" t="n">
+      <c r="F108" s="73" t="n">
         <f aca="false">'Frosted Finish – Top 3'!L9</f>
         <v>1.424</v>
       </c>
@@ -17291,7 +17548,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="28" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="B109" s="29"/>
       <c r="C109" s="29"/>
@@ -17310,7 +17567,7 @@
         <f aca="false">O109/M109</f>
         <v>1.42597333333333</v>
       </c>
-      <c r="M109" s="67" t="n">
+      <c r="M109" s="70" t="n">
         <f aca="false">SUM(M106:M108)</f>
         <v>3000</v>
       </c>
@@ -17390,140 +17647,140 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="60" t="s">
         <v>150</v>
       </c>
-      <c r="C4" s="57" t="s">
-        <v>550</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>551</v>
-      </c>
-      <c r="E4" s="57" t="s">
-        <v>552</v>
-      </c>
-      <c r="F4" s="57" t="s">
-        <v>553</v>
-      </c>
-      <c r="G4" s="57" t="s">
-        <v>554</v>
-      </c>
-      <c r="H4" s="57" t="s">
-        <v>555</v>
-      </c>
-      <c r="I4" s="57" t="s">
-        <v>556</v>
-      </c>
-      <c r="J4" s="57" t="s">
-        <v>557</v>
+      <c r="C4" s="60" t="s">
+        <v>570</v>
+      </c>
+      <c r="D4" s="60" t="s">
+        <v>571</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>572</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>573</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>574</v>
+      </c>
+      <c r="H4" s="60" t="s">
+        <v>575</v>
+      </c>
+      <c r="I4" s="60" t="s">
+        <v>576</v>
+      </c>
+      <c r="J4" s="60" t="s">
+        <v>577</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="73" t="s">
+      <c r="A5" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="73" t="s">
-        <v>558</v>
-      </c>
-      <c r="C5" s="73" t="s">
-        <v>559</v>
-      </c>
-      <c r="D5" s="73" t="s">
-        <v>560</v>
-      </c>
-      <c r="E5" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="F5" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="G5" s="73" t="s">
-        <v>561</v>
-      </c>
-      <c r="H5" s="73" t="s">
-        <v>562</v>
-      </c>
-      <c r="I5" s="73" t="s">
-        <v>563</v>
-      </c>
-      <c r="J5" s="73" t="s">
-        <v>564</v>
+      <c r="B5" s="74" t="s">
+        <v>578</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>579</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>580</v>
+      </c>
+      <c r="E5" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="F5" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="G5" s="74" t="s">
+        <v>581</v>
+      </c>
+      <c r="H5" s="74" t="s">
+        <v>582</v>
+      </c>
+      <c r="I5" s="74" t="s">
+        <v>583</v>
+      </c>
+      <c r="J5" s="74" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="73" t="s">
+      <c r="A6" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="B6" s="73" t="s">
-        <v>565</v>
-      </c>
-      <c r="C6" s="73" t="s">
-        <v>566</v>
-      </c>
-      <c r="D6" s="73" t="s">
-        <v>567</v>
-      </c>
-      <c r="E6" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="F6" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="G6" s="73" t="s">
-        <v>568</v>
-      </c>
-      <c r="H6" s="73" t="s">
-        <v>569</v>
-      </c>
-      <c r="I6" s="73" t="s">
-        <v>570</v>
-      </c>
-      <c r="J6" s="73" t="s">
-        <v>571</v>
+      <c r="B6" s="74" t="s">
+        <v>585</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>586</v>
+      </c>
+      <c r="D6" s="74" t="s">
+        <v>587</v>
+      </c>
+      <c r="E6" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="F6" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="G6" s="74" t="s">
+        <v>588</v>
+      </c>
+      <c r="H6" s="74" t="s">
+        <v>589</v>
+      </c>
+      <c r="I6" s="74" t="s">
+        <v>590</v>
+      </c>
+      <c r="J6" s="74" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="73" t="s">
-        <v>572</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>573</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>574</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>575</v>
-      </c>
-      <c r="F7" s="73" t="s">
-        <v>576</v>
-      </c>
-      <c r="G7" s="73" t="s">
-        <v>577</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>578</v>
-      </c>
-      <c r="I7" s="73" t="s">
-        <v>579</v>
-      </c>
-      <c r="J7" s="73" t="s">
-        <v>580</v>
+      <c r="B7" s="74" t="s">
+        <v>592</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>593</v>
+      </c>
+      <c r="D7" s="74" t="s">
+        <v>594</v>
+      </c>
+      <c r="E7" s="74" t="s">
+        <v>595</v>
+      </c>
+      <c r="F7" s="74" t="s">
+        <v>596</v>
+      </c>
+      <c r="G7" s="74" t="s">
+        <v>597</v>
+      </c>
+      <c r="H7" s="74" t="s">
+        <v>598</v>
+      </c>
+      <c r="I7" s="74" t="s">
+        <v>599</v>
+      </c>
+      <c r="J7" s="74" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17531,31 +17788,31 @@
         <v>201</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17563,31 +17820,31 @@
         <v>201</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>596</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17595,31 +17852,31 @@
         <v>201</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>599</v>
+        <v>619</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17627,31 +17884,31 @@
         <v>201</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17659,31 +17916,31 @@
         <v>201</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17691,31 +17948,31 @@
         <v>201</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17723,31 +17980,31 @@
         <v>201</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>629</v>
+        <v>649</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>631</v>
+        <v>651</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>632</v>
+        <v>652</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17755,31 +18012,31 @@
         <v>201</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17787,31 +18044,31 @@
         <v>201</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17819,31 +18076,31 @@
         <v>201</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17851,31 +18108,31 @@
         <v>201</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17883,127 +18140,127 @@
         <v>201</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="73" t="s">
+      <c r="A20" s="74" t="s">
         <v>206</v>
       </c>
-      <c r="B20" s="73" t="s">
-        <v>666</v>
-      </c>
-      <c r="C20" s="73" t="s">
-        <v>573</v>
-      </c>
-      <c r="D20" s="73" t="s">
-        <v>667</v>
-      </c>
-      <c r="E20" s="73" t="s">
-        <v>668</v>
-      </c>
-      <c r="F20" s="73" t="s">
-        <v>669</v>
-      </c>
-      <c r="G20" s="73" t="s">
-        <v>670</v>
-      </c>
-      <c r="H20" s="73" t="s">
-        <v>671</v>
-      </c>
-      <c r="I20" s="73" t="s">
-        <v>672</v>
-      </c>
-      <c r="J20" s="73" t="s">
-        <v>580</v>
+      <c r="B20" s="74" t="s">
+        <v>686</v>
+      </c>
+      <c r="C20" s="74" t="s">
+        <v>593</v>
+      </c>
+      <c r="D20" s="74" t="s">
+        <v>687</v>
+      </c>
+      <c r="E20" s="74" t="s">
+        <v>688</v>
+      </c>
+      <c r="F20" s="74" t="s">
+        <v>689</v>
+      </c>
+      <c r="G20" s="74" t="s">
+        <v>690</v>
+      </c>
+      <c r="H20" s="74" t="s">
+        <v>691</v>
+      </c>
+      <c r="I20" s="74" t="s">
+        <v>692</v>
+      </c>
+      <c r="J20" s="74" t="s">
+        <v>600</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="73" t="s">
+      <c r="A21" s="74" t="s">
         <v>206</v>
       </c>
-      <c r="B21" s="73" t="s">
-        <v>673</v>
-      </c>
-      <c r="C21" s="73" t="s">
-        <v>674</v>
-      </c>
-      <c r="D21" s="73" t="s">
-        <v>675</v>
-      </c>
-      <c r="E21" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="F21" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="G21" s="73" t="s">
-        <v>676</v>
-      </c>
-      <c r="H21" s="73" t="s">
-        <v>677</v>
-      </c>
-      <c r="I21" s="73" t="s">
-        <v>570</v>
-      </c>
-      <c r="J21" s="73" t="s">
-        <v>678</v>
+      <c r="B21" s="74" t="s">
+        <v>693</v>
+      </c>
+      <c r="C21" s="74" t="s">
+        <v>694</v>
+      </c>
+      <c r="D21" s="74" t="s">
+        <v>695</v>
+      </c>
+      <c r="E21" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="F21" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="G21" s="74" t="s">
+        <v>696</v>
+      </c>
+      <c r="H21" s="74" t="s">
+        <v>697</v>
+      </c>
+      <c r="I21" s="74" t="s">
+        <v>590</v>
+      </c>
+      <c r="J21" s="74" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="73" t="s">
+      <c r="A22" s="74" t="s">
         <v>206</v>
       </c>
-      <c r="B22" s="73" t="s">
-        <v>679</v>
-      </c>
-      <c r="C22" s="73" t="s">
-        <v>674</v>
-      </c>
-      <c r="D22" s="73" t="s">
-        <v>675</v>
-      </c>
-      <c r="E22" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="F22" s="73" t="s">
-        <v>500</v>
-      </c>
-      <c r="G22" s="73" t="s">
-        <v>680</v>
-      </c>
-      <c r="H22" s="73" t="s">
-        <v>681</v>
-      </c>
-      <c r="I22" s="73" t="s">
-        <v>682</v>
-      </c>
-      <c r="J22" s="73" t="s">
-        <v>683</v>
+      <c r="B22" s="74" t="s">
+        <v>699</v>
+      </c>
+      <c r="C22" s="74" t="s">
+        <v>694</v>
+      </c>
+      <c r="D22" s="74" t="s">
+        <v>695</v>
+      </c>
+      <c r="E22" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="F22" s="74" t="s">
+        <v>520</v>
+      </c>
+      <c r="G22" s="74" t="s">
+        <v>700</v>
+      </c>
+      <c r="H22" s="74" t="s">
+        <v>701</v>
+      </c>
+      <c r="I22" s="74" t="s">
+        <v>702</v>
+      </c>
+      <c r="J22" s="74" t="s">
+        <v>703</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18011,31 +18268,31 @@
         <v>206</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18043,31 +18300,31 @@
         <v>206</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18075,31 +18332,31 @@
         <v>206</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18107,31 +18364,31 @@
         <v>206</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18139,31 +18396,31 @@
         <v>206</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18171,28 +18428,28 @@
         <v>206</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>591</v>
+        <v>611</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="J28" s="6"/>
     </row>
